--- a/Financial Analysis/WISE.xlsx
+++ b/Financial Analysis/WISE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1C6A95-4AD3-4F8F-87AE-C68D811AE9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447765F4-0D3E-43B3-A53F-6B685C25AA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DF2D7ED4-E95E-4EA0-AAC3-7C5D2EE7EFC0}"/>
   </bookViews>
@@ -187,9 +187,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Undervalued</t>
-  </si>
-  <si>
     <t>Q1/Q3 cross-border revenue</t>
   </si>
   <si>
@@ -218,6 +215,9 @@
   </si>
   <si>
     <t>Total card and other revenue</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -736,14 +736,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>8.98</v>
+        <v>11.17</v>
       </c>
       <c r="F3" s="6">
         <v>45730</v>
       </c>
       <c r="G3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45737</v>
+        <v>45804</v>
       </c>
       <c r="H3" s="6">
         <v>45762</v>
@@ -766,7 +766,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>9241.3179999999993</v>
+        <v>11495.046999999999</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>4372.1179999999995</v>
+        <v>6625.8469999999988</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +985,7 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="29" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="30" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="31" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="32" spans="1:147" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AE41" s="1">
         <f>Main!D3</f>
-        <v>8.98</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="42" spans="2:31" x14ac:dyDescent="0.3">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AE42" s="11">
         <f>AE40/AE41-1</f>
-        <v>0.29282192477201852</v>
+        <v>3.9350123943842963E-2</v>
       </c>
     </row>
     <row r="43" spans="2:31" x14ac:dyDescent="0.3">
@@ -4343,7 +4343,7 @@
         <v>52</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/WISE.xlsx
+++ b/Financial Analysis/WISE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447765F4-0D3E-43B3-A53F-6B685C25AA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4901FB-EDCA-4971-844B-9446C54A7208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DF2D7ED4-E95E-4EA0-AAC3-7C5D2EE7EFC0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>Price</t>
   </si>
@@ -217,7 +217,13 @@
     <t>Total card and other revenue</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -227,7 +233,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +250,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -294,6 +309,12 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,14 +386,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
@@ -389,8 +410,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12763500" y="15240"/>
-          <a:ext cx="0" cy="6012180"/>
+          <a:off x="15544800" y="15240"/>
+          <a:ext cx="0" cy="8389620"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -736,17 +757,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>11.17</v>
+        <v>10.3</v>
       </c>
       <c r="F3" s="6">
-        <v>45730</v>
+        <v>45824</v>
       </c>
       <c r="G3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45825</v>
       </c>
       <c r="H3" s="6">
-        <v>45762</v>
+        <v>45967</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.3">
@@ -754,10 +775,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>1029.0999999999999</v>
+        <f>1032.2</f>
+        <v>1032.2</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.3">
@@ -766,7 +788,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>11495.046999999999</v>
+        <v>10631.660000000002</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
@@ -774,11 +796,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <f>4029.6+2.6+1061.2</f>
-        <v>5093.3999999999996</v>
+        <f>4654.9+1430.2</f>
+        <v>6085.0999999999995</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
@@ -786,11 +808,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <f>14.8+209.4</f>
-        <v>224.20000000000002</v>
+        <f>1.3+98.1</f>
+        <v>99.399999999999991</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
@@ -799,7 +821,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>4869.2</v>
+        <v>5985.7</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
@@ -808,7 +830,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>6625.8469999999988</v>
+        <v>4645.9600000000019</v>
       </c>
     </row>
   </sheetData>
@@ -818,17 +840,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64CDCC9C-14C1-4CAB-9334-0C94F06D7EEC}">
-  <dimension ref="A1:EQ43"/>
+  <dimension ref="A1:ES43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="28" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.77734375" customWidth="1"/>
-    <col min="31" max="31" width="18.109375" customWidth="1"/>
+    <col min="11" max="12" width="10.5546875" customWidth="1"/>
+    <col min="14" max="30" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.77734375" customWidth="1"/>
+    <col min="33" max="33" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="C1" s="3">
         <v>44469</v>
       </c>
@@ -853,60 +876,66 @@
       <c r="J1" s="3">
         <v>45747</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="3">
+        <v>45930</v>
+      </c>
       <c r="L1" s="3">
+        <v>46112</v>
+      </c>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3">
         <v>43555</v>
       </c>
-      <c r="M1" s="3">
+      <c r="O1" s="3">
         <v>43921</v>
       </c>
-      <c r="N1" s="3">
+      <c r="P1" s="3">
         <v>44286</v>
       </c>
-      <c r="O1" s="3">
+      <c r="Q1" s="3">
         <v>44651</v>
       </c>
-      <c r="P1" s="3">
+      <c r="R1" s="3">
         <v>45016</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="S1" s="3">
         <v>45382</v>
       </c>
-      <c r="R1" s="3">
+      <c r="T1" s="3">
         <v>45747</v>
       </c>
-      <c r="S1" s="3">
+      <c r="U1" s="3">
         <v>46112</v>
       </c>
-      <c r="T1" s="3">
+      <c r="V1" s="3">
         <v>46477</v>
       </c>
-      <c r="U1" s="3">
+      <c r="W1" s="3">
         <v>46843</v>
       </c>
-      <c r="V1" s="3">
+      <c r="X1" s="3">
         <v>47208</v>
       </c>
-      <c r="W1" s="3">
+      <c r="Y1" s="3">
         <v>47573</v>
       </c>
-      <c r="X1" s="3">
+      <c r="Z1" s="3">
         <v>47938</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="AA1" s="3">
         <v>48304</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="AB1" s="3">
         <v>48669</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AC1" s="3">
         <v>49034</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AD1" s="3">
         <v>49399</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
@@ -931,59 +960,65 @@
       <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
+      <c r="K2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2">
         <v>2019</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>2020</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>2021</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>2022</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>2023</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>2024</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>2025</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>2026</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>2027</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>2028</v>
       </c>
-      <c r="V2">
+      <c r="X2">
         <v>2029</v>
       </c>
-      <c r="W2">
+      <c r="Y2">
         <v>2030</v>
       </c>
-      <c r="X2">
+      <c r="Z2">
         <v>2031</v>
       </c>
-      <c r="Y2">
+      <c r="AA2">
         <v>2032</v>
       </c>
-      <c r="Z2">
+      <c r="AB2">
         <v>2033</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>2034</v>
       </c>
-      <c r="AB2">
+      <c r="AD2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>53</v>
       </c>
@@ -1005,8 +1040,10 @@
       <c r="J3" s="12">
         <v>212.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -1025,12 +1062,14 @@
       <c r="I4" s="12">
         <v>207.9</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="13">
         <f>H4*1.03</f>
         <v>210.738</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>61</v>
       </c>
@@ -1057,16 +1096,18 @@
         <f t="shared" si="0"/>
         <v>423.63800000000003</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="S5" s="2">
         <f>G5+H5</f>
         <v>795.19999999999993</v>
       </c>
-      <c r="R5" s="2">
+      <c r="T5" s="2">
         <f>I5+J5</f>
         <v>842.73800000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>55</v>
       </c>
@@ -1088,8 +1129,10 @@
       <c r="J6" s="12">
         <v>97.8</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>56</v>
       </c>
@@ -1108,12 +1151,14 @@
       <c r="I7" s="12">
         <v>92.8</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <f>H7*1.35</f>
         <v>98.01</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>62</v>
       </c>
@@ -1140,16 +1185,18 @@
         <f t="shared" si="1"/>
         <v>195.81</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="S8" s="2">
         <f>G8+H8</f>
         <v>256.8</v>
       </c>
-      <c r="R8" s="2">
+      <c r="T8" s="2">
         <f>I8+J8</f>
         <v>368.61</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1158,10 +1205,12 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -1169,86 +1218,87 @@
         <v>256.3</v>
       </c>
       <c r="D10" s="2">
-        <f>O10-C10</f>
+        <f>Q10-C10</f>
         <v>303.59999999999997</v>
       </c>
       <c r="E10" s="2">
         <v>397.4</v>
       </c>
       <c r="F10" s="2">
-        <f>P10-E10</f>
+        <f>R10-E10</f>
         <v>448.70000000000005</v>
       </c>
       <c r="G10" s="2">
         <v>498.2</v>
       </c>
       <c r="H10" s="2">
-        <f>Q10-G10</f>
+        <f>S10-G10</f>
         <v>553.79999999999995</v>
       </c>
       <c r="I10" s="2">
         <v>591.9</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="14">
         <f>J5+J8</f>
         <v>619.44800000000009</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2">
         <v>559.9</v>
       </c>
-      <c r="P10" s="2">
+      <c r="R10" s="2">
         <v>846.1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="S10" s="2">
         <v>1052</v>
       </c>
-      <c r="R10" s="2">
-        <f>SUM(I10:J10)</f>
-        <v>1211.348</v>
-      </c>
-      <c r="S10" s="2">
-        <f>R10*1.12</f>
-        <v>1356.7097600000002</v>
-      </c>
       <c r="T10" s="2">
-        <f>S10*1.1</f>
-        <v>1492.3807360000003</v>
+        <v>1211.9000000000001</v>
       </c>
       <c r="U10" s="2">
-        <f>T10*1.07</f>
-        <v>1596.8473875200004</v>
+        <f>T10*1.12</f>
+        <v>1357.3280000000002</v>
       </c>
       <c r="V10" s="2">
-        <f>U10*1.05</f>
-        <v>1676.6897568960005</v>
+        <f>U10*1.1</f>
+        <v>1493.0608000000004</v>
       </c>
       <c r="W10" s="2">
-        <f>V10*1.04</f>
-        <v>1743.7573471718406</v>
+        <f>V10*1.07</f>
+        <v>1597.5750560000006</v>
       </c>
       <c r="X10" s="2">
-        <f>W10*1.03</f>
-        <v>1796.0700675869959</v>
+        <f>W10*1.05</f>
+        <v>1677.4538088000006</v>
       </c>
       <c r="Y10" s="2">
-        <f>X10*1.02</f>
-        <v>1831.9914689387358</v>
+        <f>X10*1.04</f>
+        <v>1744.5519611520008</v>
       </c>
       <c r="Z10" s="2">
-        <f t="shared" ref="Z10:AB10" si="2">Y10*1.02</f>
-        <v>1868.6312983175105</v>
+        <f>Y10*1.03</f>
+        <v>1796.8885199865608</v>
       </c>
       <c r="AA10" s="2">
+        <f>Z10*1.02</f>
+        <v>1832.8262903862922</v>
+      </c>
+      <c r="AB10" s="2">
+        <f t="shared" ref="AB10:AD10" si="2">AA10*1.02</f>
+        <v>1869.4828161940181</v>
+      </c>
+      <c r="AC10" s="2">
         <f t="shared" si="2"/>
-        <v>1906.0039242838607</v>
-      </c>
-      <c r="AB10" s="2">
+        <v>1906.8724725178986</v>
+      </c>
+      <c r="AD10" s="2">
         <f t="shared" si="2"/>
-        <v>1944.1240027695378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+        <v>1945.0099219682565</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1257,7 +1307,7 @@
         <v>-1.2000000000000002</v>
       </c>
       <c r="D11" s="2">
-        <f>O11-C11</f>
+        <f>Q11-C11</f>
         <v>-1.6</v>
       </c>
       <c r="E11" s="2">
@@ -1265,81 +1315,82 @@
         <v>18.7</v>
       </c>
       <c r="F11" s="2">
-        <f>P11-E11</f>
+        <f>R11-E11</f>
         <v>117.8</v>
       </c>
       <c r="G11" s="2">
         <v>211.1</v>
       </c>
       <c r="H11" s="2">
-        <f>Q11-G11</f>
+        <f>S11-G11</f>
         <v>274.10000000000002</v>
       </c>
       <c r="I11" s="2">
         <v>300.7</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="14">
         <f>H11*1.28</f>
         <v>350.84800000000001</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2">
         <f>3.9-6.7</f>
         <v>-2.8000000000000003</v>
       </c>
-      <c r="P11" s="2">
+      <c r="R11" s="2">
         <f>140.2-3.7</f>
         <v>136.5</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="S11" s="2">
         <v>485.2</v>
       </c>
-      <c r="R11" s="2">
-        <f>SUM(I11:J11)</f>
-        <v>651.548</v>
-      </c>
-      <c r="S11" s="2">
-        <f>R11*1.15</f>
-        <v>749.28019999999992</v>
-      </c>
       <c r="T11" s="2">
-        <f>S11*1.11</f>
-        <v>831.70102199999997</v>
+        <v>594.29999999999995</v>
       </c>
       <c r="U11" s="2">
-        <f>T11*1.07</f>
-        <v>889.92009354000004</v>
+        <f>T11*1.15</f>
+        <v>683.44499999999994</v>
       </c>
       <c r="V11" s="2">
-        <f>U11*1.03</f>
-        <v>916.61769634620009</v>
+        <f>U11*1.11</f>
+        <v>758.62395000000004</v>
       </c>
       <c r="W11" s="2">
-        <f>V11*1.02</f>
-        <v>934.95005027312413</v>
+        <f>V11*1.07</f>
+        <v>811.72762650000004</v>
       </c>
       <c r="X11" s="2">
-        <f t="shared" ref="X11:AB11" si="3">W11*1.02</f>
-        <v>953.64905127858663</v>
+        <f>W11*1.03</f>
+        <v>836.07945529500012</v>
       </c>
       <c r="Y11" s="2">
-        <f t="shared" si="3"/>
-        <v>972.72203230415835</v>
+        <f>X11*1.02</f>
+        <v>852.80104440090008</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" si="3"/>
-        <v>992.17647295024153</v>
+        <f t="shared" ref="Z11:AD11" si="3">Y11*1.02</f>
+        <v>869.85706528891808</v>
       </c>
       <c r="AA11" s="2">
         <f t="shared" si="3"/>
-        <v>1012.0200024092463</v>
+        <v>887.25420659469648</v>
       </c>
       <c r="AB11" s="2">
         <f t="shared" si="3"/>
-        <v>1032.2604024574314</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>904.9992907265904</v>
+      </c>
+      <c r="AC11" s="2">
+        <f t="shared" si="3"/>
+        <v>923.09927654112221</v>
+      </c>
+      <c r="AD11" s="2">
+        <f t="shared" si="3"/>
+        <v>941.56126207194472</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12"/>
       <c r="B12" s="8" t="s">
         <v>23</v>
@@ -1372,77 +1423,79 @@
         <f t="shared" ref="I12:J12" si="5">I10+I11</f>
         <v>892.59999999999991</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="15">
         <f t="shared" si="5"/>
         <v>970.29600000000005</v>
       </c>
-      <c r="L12" s="9">
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="N12" s="9">
         <v>177.9</v>
       </c>
-      <c r="M12" s="9">
+      <c r="O12" s="9">
         <v>302.60000000000002</v>
       </c>
-      <c r="N12" s="9">
+      <c r="P12" s="9">
         <v>421</v>
-      </c>
-      <c r="O12" s="9">
-        <f>O10+O11</f>
-        <v>557.1</v>
-      </c>
-      <c r="P12" s="9">
-        <f>P10+P11</f>
-        <v>982.6</v>
       </c>
       <c r="Q12" s="9">
         <f>Q10+Q11</f>
-        <v>1537.2</v>
+        <v>557.1</v>
       </c>
       <c r="R12" s="9">
         <f>R10+R11</f>
-        <v>1862.896</v>
+        <v>982.6</v>
       </c>
       <c r="S12" s="9">
         <f>S10+S11</f>
-        <v>2105.9899599999999</v>
+        <v>1537.2</v>
       </c>
       <c r="T12" s="9">
-        <f t="shared" ref="T12:AB12" si="6">T10+T11</f>
-        <v>2324.0817580000003</v>
+        <f>T10+T11</f>
+        <v>1806.2</v>
       </c>
       <c r="U12" s="9">
-        <f t="shared" si="6"/>
-        <v>2486.7674810600006</v>
+        <f>U10+U11</f>
+        <v>2040.7730000000001</v>
       </c>
       <c r="V12" s="9">
-        <f t="shared" si="6"/>
-        <v>2593.3074532422006</v>
+        <f t="shared" ref="V12:AD12" si="6">V10+V11</f>
+        <v>2251.6847500000003</v>
       </c>
       <c r="W12" s="9">
         <f t="shared" si="6"/>
-        <v>2678.707397444965</v>
+        <v>2409.3026825000006</v>
       </c>
       <c r="X12" s="9">
         <f t="shared" si="6"/>
-        <v>2749.7191188655825</v>
+        <v>2513.533264095001</v>
       </c>
       <c r="Y12" s="9">
         <f t="shared" si="6"/>
-        <v>2804.7135012428944</v>
+        <v>2597.3530055529009</v>
       </c>
       <c r="Z12" s="9">
         <f t="shared" si="6"/>
-        <v>2860.8077712677523</v>
+        <v>2666.7455852754788</v>
       </c>
       <c r="AA12" s="9">
         <f t="shared" si="6"/>
-        <v>2918.0239266931071</v>
+        <v>2720.0804969809888</v>
       </c>
       <c r="AB12" s="9">
         <f t="shared" si="6"/>
-        <v>2976.3844052269692</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+        <v>2774.4821069206087</v>
+      </c>
+      <c r="AC12" s="9">
+        <f t="shared" si="6"/>
+        <v>2829.971749059021</v>
+      </c>
+      <c r="AD12" s="9">
+        <f t="shared" si="6"/>
+        <v>2886.5711840402014</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>20</v>
       </c>
@@ -1450,48 +1503,47 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <f>O13-C13</f>
+        <f>Q13-C13</f>
         <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f>P13-E13</f>
+        <f>R13-E13</f>
         <v>18.399999999999999</v>
       </c>
       <c r="G13" s="2">
         <v>53.3</v>
       </c>
       <c r="H13" s="2">
-        <f>Q13-G13</f>
+        <f>S13-G13</f>
         <v>71.600000000000009</v>
       </c>
       <c r="I13" s="2">
         <v>84.8</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="14">
         <f>J11*0.26</f>
         <v>91.220480000000009</v>
       </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2">
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2">
         <v>0</v>
       </c>
-      <c r="P13" s="2">
+      <c r="R13" s="2">
         <v>18.399999999999999</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="S13" s="2">
         <v>124.9</v>
       </c>
-      <c r="R13" s="2">
-        <f>SUM(I13:J13)</f>
-        <v>176.02048000000002</v>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
+      <c r="T13" s="2">
+        <v>161.19999999999999</v>
+      </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
@@ -1500,8 +1552,10 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -1509,54 +1563,53 @@
         <v>81.2</v>
       </c>
       <c r="D14" s="2">
-        <f>O14-C14</f>
+        <f>Q14-C14</f>
         <v>104.60000000000001</v>
       </c>
       <c r="E14" s="2">
         <v>148.5</v>
       </c>
       <c r="F14" s="2">
-        <f>P14-E14</f>
+        <f>R14-E14</f>
         <v>159.69999999999999</v>
       </c>
       <c r="G14" s="2">
         <v>160.69999999999999</v>
       </c>
       <c r="H14" s="2">
-        <f>Q14-G14</f>
+        <f>S14-G14</f>
         <v>146.69999999999999</v>
       </c>
       <c r="I14" s="2">
         <v>152.9</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="14">
         <f>J10*0.26</f>
         <v>161.05648000000002</v>
       </c>
-      <c r="L14" s="2">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="N14" s="2">
         <v>66.5</v>
       </c>
-      <c r="M14" s="2">
+      <c r="O14" s="2">
         <v>111.4</v>
       </c>
-      <c r="N14" s="2">
+      <c r="P14" s="2">
         <v>151.69999999999999</v>
       </c>
-      <c r="O14" s="2">
+      <c r="Q14" s="2">
         <v>185.8</v>
       </c>
-      <c r="P14" s="2">
+      <c r="R14" s="2">
         <v>308.2</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="S14" s="2">
         <v>307.39999999999998</v>
       </c>
-      <c r="R14" s="2">
-        <f>SUM(I14:J14)</f>
-        <v>313.95648000000006</v>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
+      <c r="T14" s="2">
+        <v>328.1</v>
+      </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
@@ -1565,8 +1618,10 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>22</v>
       </c>
@@ -1574,54 +1629,53 @@
         <v>1.3</v>
       </c>
       <c r="D15" s="2">
-        <f>O15-C15</f>
+        <f>Q15-C15</f>
         <v>0.90000000000000013</v>
       </c>
       <c r="E15" s="2">
         <v>5.2</v>
       </c>
       <c r="F15" s="2">
-        <f>P15-E15</f>
+        <f>R15-E15</f>
         <v>12.600000000000001</v>
       </c>
       <c r="G15" s="2">
         <v>6.4</v>
       </c>
       <c r="H15" s="2">
-        <f>Q15-G15</f>
+        <f>S15-G15</f>
         <v>6.1</v>
       </c>
       <c r="I15" s="2">
         <v>4.5</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="14">
         <f>J10*0.01</f>
         <v>6.1944800000000013</v>
       </c>
-      <c r="L15" s="2">
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="N15" s="2">
         <v>1</v>
       </c>
-      <c r="M15" s="2">
+      <c r="O15" s="2">
         <v>3.1</v>
       </c>
-      <c r="N15" s="2">
+      <c r="P15" s="2">
         <v>8.8000000000000007</v>
       </c>
-      <c r="O15" s="2">
+      <c r="Q15" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="P15" s="2">
+      <c r="R15" s="2">
         <v>17.8</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="S15" s="2">
         <v>12.5</v>
       </c>
-      <c r="R15" s="2">
-        <f>SUM(I15:J15)</f>
-        <v>10.694480000000002</v>
-      </c>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
+      <c r="T15" s="2">
+        <v>9.1</v>
+      </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
@@ -1630,8 +1684,10 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>24</v>
       </c>
@@ -1663,80 +1719,82 @@
         <f t="shared" ref="I16:J16" si="8">I13+I14+I15</f>
         <v>242.2</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="14">
         <f t="shared" si="8"/>
         <v>258.47144000000003</v>
       </c>
-      <c r="L16" s="2">
-        <f t="shared" ref="L16:R16" si="9">L13+L14+L15</f>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="N16" s="2">
+        <f t="shared" ref="N16:T16" si="9">N13+N14+N15</f>
         <v>67.5</v>
       </c>
-      <c r="M16" s="2">
+      <c r="O16" s="2">
         <f t="shared" si="9"/>
         <v>114.5</v>
       </c>
-      <c r="N16" s="2">
+      <c r="P16" s="2">
         <f t="shared" si="9"/>
         <v>160.5</v>
       </c>
-      <c r="O16" s="2">
+      <c r="Q16" s="2">
         <f t="shared" si="9"/>
         <v>188</v>
       </c>
-      <c r="P16" s="2">
+      <c r="R16" s="2">
         <f t="shared" si="9"/>
         <v>344.4</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="S16" s="2">
         <f t="shared" si="9"/>
         <v>444.79999999999995</v>
       </c>
-      <c r="R16" s="2">
+      <c r="T16" s="2">
         <f t="shared" si="9"/>
-        <v>500.67144000000008</v>
-      </c>
-      <c r="S16" s="2">
-        <f>S12-S17</f>
-        <v>547.55738960000008</v>
-      </c>
-      <c r="T16" s="2">
-        <f t="shared" ref="T16:AB16" si="10">T12-T17</f>
-        <v>604.26125708000018</v>
+        <v>498.40000000000003</v>
       </c>
       <c r="U16" s="2">
-        <f t="shared" si="10"/>
-        <v>646.55954507560023</v>
+        <f>U12-U17</f>
+        <v>530.60098000000016</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" si="10"/>
-        <v>674.25993784297225</v>
+        <f t="shared" ref="V16:AD16" si="10">V12-V17</f>
+        <v>585.43803500000013</v>
       </c>
       <c r="W16" s="2">
         <f t="shared" si="10"/>
-        <v>696.46392333569088</v>
+        <v>626.41869745000008</v>
       </c>
       <c r="X16" s="2">
         <f t="shared" si="10"/>
-        <v>714.92697090505158</v>
+        <v>653.51864866470032</v>
       </c>
       <c r="Y16" s="2">
         <f t="shared" si="10"/>
-        <v>729.22551032315278</v>
+        <v>675.31178144375417</v>
       </c>
       <c r="Z16" s="2">
         <f t="shared" si="10"/>
-        <v>743.81002052961549</v>
+        <v>693.35385217162457</v>
       </c>
       <c r="AA16" s="2">
         <f t="shared" si="10"/>
-        <v>758.68622094020793</v>
+        <v>707.22092921505714</v>
       </c>
       <c r="AB16" s="2">
         <f t="shared" si="10"/>
-        <v>773.85994535901182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:147" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>721.36534779935846</v>
+      </c>
+      <c r="AC16" s="2">
+        <f t="shared" si="10"/>
+        <v>735.79265475534567</v>
+      </c>
+      <c r="AD16" s="2">
+        <f t="shared" si="10"/>
+        <v>750.50850785045259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17"/>
       <c r="B17" s="8" t="s">
         <v>25</v>
@@ -1769,80 +1827,82 @@
         <f t="shared" ref="I17:J17" si="12">I12-I16</f>
         <v>650.39999999999986</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="15">
         <f t="shared" si="12"/>
         <v>711.82456000000002</v>
       </c>
-      <c r="L17" s="9">
-        <f t="shared" ref="L17:R17" si="13">L12-L16</f>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="N17" s="9">
+        <f t="shared" ref="N17:T17" si="13">N12-N16</f>
         <v>110.4</v>
       </c>
-      <c r="M17" s="9">
+      <c r="O17" s="9">
         <f t="shared" si="13"/>
         <v>188.10000000000002</v>
       </c>
-      <c r="N17" s="9">
+      <c r="P17" s="9">
         <f t="shared" si="13"/>
         <v>260.5</v>
       </c>
-      <c r="O17" s="9">
+      <c r="Q17" s="9">
         <f t="shared" si="13"/>
         <v>369.1</v>
       </c>
-      <c r="P17" s="9">
+      <c r="R17" s="9">
         <f t="shared" si="13"/>
         <v>638.20000000000005</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="S17" s="9">
         <f t="shared" si="13"/>
         <v>1092.4000000000001</v>
       </c>
-      <c r="R17" s="9">
+      <c r="T17" s="9">
         <f t="shared" si="13"/>
-        <v>1362.2245599999999</v>
-      </c>
-      <c r="S17" s="9">
-        <f>S12*0.74</f>
-        <v>1558.4325703999998</v>
-      </c>
-      <c r="T17" s="9">
-        <f t="shared" ref="T17:AB17" si="14">T12*0.74</f>
-        <v>1719.8205009200001</v>
+        <v>1307.8</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" si="14"/>
-        <v>1840.2079359844004</v>
+        <f>U12*0.74</f>
+        <v>1510.17202</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" si="14"/>
-        <v>1919.0475153992284</v>
+        <f t="shared" ref="V17:AD17" si="14">V12*0.74</f>
+        <v>1666.2467150000002</v>
       </c>
       <c r="W17" s="9">
         <f t="shared" si="14"/>
-        <v>1982.2434741092741</v>
+        <v>1782.8839850500005</v>
       </c>
       <c r="X17" s="9">
         <f t="shared" si="14"/>
-        <v>2034.7921479605309</v>
+        <v>1860.0146154303006</v>
       </c>
       <c r="Y17" s="9">
         <f t="shared" si="14"/>
-        <v>2075.4879909197416</v>
+        <v>1922.0412241091467</v>
       </c>
       <c r="Z17" s="9">
         <f t="shared" si="14"/>
-        <v>2116.9977507381368</v>
+        <v>1973.3917331038542</v>
       </c>
       <c r="AA17" s="9">
         <f t="shared" si="14"/>
-        <v>2159.3377057528992</v>
+        <v>2012.8595677659316</v>
       </c>
       <c r="AB17" s="9">
         <f t="shared" si="14"/>
-        <v>2202.5244598679574</v>
-      </c>
-    </row>
-    <row r="18" spans="1:147" x14ac:dyDescent="0.3">
+        <v>2053.1167591212502</v>
+      </c>
+      <c r="AC17" s="9">
+        <f t="shared" si="14"/>
+        <v>2094.1790943036754</v>
+      </c>
+      <c r="AD17" s="9">
+        <f t="shared" si="14"/>
+        <v>2136.0626761897488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>26</v>
       </c>
@@ -1850,94 +1910,95 @@
         <v>152.19999999999999</v>
       </c>
       <c r="D18" s="2">
-        <f>O18-C18</f>
+        <f>Q18-C18</f>
         <v>169.2</v>
       </c>
       <c r="E18" s="2">
         <v>214.9</v>
       </c>
       <c r="F18" s="2">
-        <f>P18-E18</f>
+        <f>R18-E18</f>
         <v>279.60000000000002</v>
       </c>
       <c r="G18" s="2">
         <v>296.5</v>
       </c>
       <c r="H18" s="2">
-        <f>Q18-G18</f>
+        <f>S18-G18</f>
         <v>319.39999999999998</v>
       </c>
       <c r="I18" s="2">
         <v>366.7</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="14">
         <f>H18*1.19</f>
         <v>380.08599999999996</v>
       </c>
-      <c r="L18" s="2">
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="N18" s="2">
         <v>99.5</v>
       </c>
-      <c r="M18" s="2">
+      <c r="O18" s="2">
         <v>168.8</v>
       </c>
-      <c r="N18" s="2">
+      <c r="P18" s="2">
         <v>217.5</v>
       </c>
-      <c r="O18" s="2">
+      <c r="Q18" s="2">
         <v>321.39999999999998</v>
       </c>
-      <c r="P18" s="2">
+      <c r="R18" s="2">
         <v>494.5</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="S18" s="2">
         <v>615.9</v>
       </c>
-      <c r="R18" s="2">
-        <f>SUM(I18:J18)</f>
-        <v>746.78599999999994</v>
-      </c>
-      <c r="S18" s="2">
-        <f>R18*1.15</f>
-        <v>858.80389999999989</v>
-      </c>
       <c r="T18" s="2">
-        <f>S18*1.12</f>
-        <v>961.86036799999999</v>
+        <v>768.6</v>
       </c>
       <c r="U18" s="2">
-        <f>T18*1.08</f>
-        <v>1038.8091974400002</v>
+        <f>T18*1.15</f>
+        <v>883.89</v>
       </c>
       <c r="V18" s="2">
-        <f>U18*1.04</f>
-        <v>1080.3615653376003</v>
+        <f>U18*1.12</f>
+        <v>989.95680000000004</v>
       </c>
       <c r="W18" s="2">
-        <f>V18*1.03</f>
-        <v>1112.7724122977284</v>
+        <f>V18*1.08</f>
+        <v>1069.1533440000001</v>
       </c>
       <c r="X18" s="2">
-        <f>W18*1.02</f>
-        <v>1135.0278605436829</v>
+        <f>W18*1.04</f>
+        <v>1111.9194777600001</v>
       </c>
       <c r="Y18" s="2">
-        <f t="shared" ref="Y18:AB18" si="15">X18*1.02</f>
-        <v>1157.7284177545566</v>
+        <f>X18*1.03</f>
+        <v>1145.2770620928002</v>
       </c>
       <c r="Z18" s="2">
-        <f t="shared" si="15"/>
-        <v>1180.8829861096478</v>
+        <f>Y18*1.02</f>
+        <v>1168.1826033346563</v>
       </c>
       <c r="AA18" s="2">
-        <f t="shared" si="15"/>
-        <v>1204.5006458318408</v>
+        <f t="shared" ref="AA18:AD18" si="15">Z18*1.02</f>
+        <v>1191.5462554013495</v>
       </c>
       <c r="AB18" s="2">
         <f t="shared" si="15"/>
-        <v>1228.5906587484776</v>
-      </c>
-    </row>
-    <row r="19" spans="1:147" x14ac:dyDescent="0.3">
+        <v>1215.3771805093766</v>
+      </c>
+      <c r="AC18" s="2">
+        <f t="shared" si="15"/>
+        <v>1239.6847241195642</v>
+      </c>
+      <c r="AD18" s="2">
+        <f t="shared" si="15"/>
+        <v>1264.4784186019556</v>
+      </c>
+    </row>
+    <row r="19" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>27</v>
       </c>
@@ -1945,95 +2006,96 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <f>O19-C19</f>
+        <f>Q19-C19</f>
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <v>-0.3</v>
       </c>
       <c r="F19" s="2">
-        <f>P19-E19</f>
+        <f>R19-E19</f>
         <v>-2.5</v>
       </c>
       <c r="G19" s="2">
         <v>-7.3</v>
       </c>
       <c r="H19" s="2">
-        <f>Q19-G19</f>
+        <f>S19-G19</f>
         <v>-12.399999999999999</v>
       </c>
       <c r="I19" s="2">
         <v>-15.9</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="14">
         <v>-18</v>
       </c>
-      <c r="L19" s="2">
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="N19" s="2">
         <v>-0.9</v>
       </c>
-      <c r="M19" s="2">
+      <c r="O19" s="2">
         <f>-5.4+1.3</f>
         <v>-4.1000000000000005</v>
       </c>
-      <c r="N19" s="2">
+      <c r="P19" s="2">
         <f>-1.9+3.8</f>
         <v>1.9</v>
       </c>
-      <c r="O19" s="2">
+      <c r="Q19" s="2">
         <v>0</v>
       </c>
-      <c r="P19" s="2">
+      <c r="R19" s="2">
         <v>-2.8</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="S19" s="2">
         <v>-19.7</v>
       </c>
-      <c r="R19" s="2">
-        <f>SUM(I19:J19)</f>
-        <v>-33.9</v>
-      </c>
-      <c r="S19" s="2">
-        <f>R19*1.03</f>
-        <v>-34.917000000000002</v>
-      </c>
       <c r="T19" s="2">
-        <f t="shared" ref="T19:AB19" si="16">S19*1.03</f>
-        <v>-35.964510000000004</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="U19" s="2">
-        <f t="shared" si="16"/>
-        <v>-37.043445300000002</v>
+        <f>T19*1.03</f>
+        <v>-34.298999999999999</v>
       </c>
       <c r="V19" s="2">
-        <f t="shared" si="16"/>
-        <v>-38.154748659000006</v>
+        <f t="shared" ref="V19:AD19" si="16">U19*1.03</f>
+        <v>-35.327970000000001</v>
       </c>
       <c r="W19" s="2">
         <f t="shared" si="16"/>
-        <v>-39.299391118770011</v>
+        <v>-36.387809099999998</v>
       </c>
       <c r="X19" s="2">
         <f t="shared" si="16"/>
-        <v>-40.478372852333109</v>
+        <v>-37.479443373000002</v>
       </c>
       <c r="Y19" s="2">
         <f t="shared" si="16"/>
-        <v>-41.692724037903105</v>
+        <v>-38.603826674190003</v>
       </c>
       <c r="Z19" s="2">
         <f t="shared" si="16"/>
-        <v>-42.9435057590402</v>
+        <v>-39.761941474415707</v>
       </c>
       <c r="AA19" s="2">
         <f t="shared" si="16"/>
-        <v>-44.23181093181141</v>
+        <v>-40.954799718648182</v>
       </c>
       <c r="AB19" s="2">
         <f t="shared" si="16"/>
-        <v>-45.558765259765757</v>
-      </c>
-    </row>
-    <row r="20" spans="1:147" x14ac:dyDescent="0.3">
+        <v>-42.183443710207627</v>
+      </c>
+      <c r="AC19" s="2">
+        <f t="shared" si="16"/>
+        <v>-43.44894702151386</v>
+      </c>
+      <c r="AD19" s="2">
+        <f t="shared" si="16"/>
+        <v>-44.752415432159275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>28</v>
       </c>
@@ -2041,57 +2103,52 @@
         <v>-0.9</v>
       </c>
       <c r="D20" s="2">
-        <f>O20-C20</f>
+        <f>Q20-C20</f>
         <v>-9.9999999999999978E-2</v>
       </c>
       <c r="E20" s="2">
         <v>-7.2</v>
       </c>
       <c r="F20" s="2">
-        <f>P20-E20</f>
+        <f>R20-E20</f>
         <v>-3.4999999999999991</v>
       </c>
       <c r="G20" s="2">
         <v>-3.9</v>
       </c>
       <c r="H20" s="2">
-        <f>Q20-G20</f>
+        <f>S20-G20</f>
         <v>-1.8000000000000003</v>
       </c>
       <c r="I20" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="14">
         <v>-3</v>
       </c>
-      <c r="L20" s="2">
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="N20" s="2">
         <v>-0.4</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O20" s="2">
         <v>0.2</v>
       </c>
-      <c r="N20" s="2">
+      <c r="P20" s="2">
         <v>-3.8</v>
       </c>
-      <c r="O20" s="2">
+      <c r="Q20" s="2">
         <f>-5.8+4.8</f>
         <v>-1</v>
       </c>
-      <c r="P20" s="2">
+      <c r="R20" s="2">
         <v>-10.7</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="S20" s="2">
         <v>-5.7</v>
       </c>
-      <c r="R20" s="2">
-        <f>SUM(I20:J20)</f>
-        <v>-5.3</v>
-      </c>
-      <c r="S20" s="2">
-        <v>0</v>
-      </c>
       <c r="T20" s="2">
-        <v>0</v>
+        <v>-7.1</v>
       </c>
       <c r="U20" s="2">
         <v>0</v>
@@ -2117,8 +2174,14 @@
       <c r="AB20" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:147" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21"/>
       <c r="B21" s="8" t="s">
         <v>29</v>
@@ -2151,80 +2214,82 @@
         <f t="shared" si="17"/>
         <v>301.89999999999986</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="15">
         <f t="shared" si="17"/>
         <v>352.73856000000006</v>
       </c>
-      <c r="L21" s="9">
-        <f t="shared" ref="L21:S21" si="18">L17-L18-L19-L20</f>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="N21" s="9">
+        <f t="shared" ref="N21:U21" si="18">N17-N18-N19-N20</f>
         <v>12.200000000000006</v>
       </c>
-      <c r="M21" s="9">
+      <c r="O21" s="9">
         <f t="shared" si="18"/>
         <v>23.200000000000014</v>
       </c>
-      <c r="N21" s="9">
+      <c r="P21" s="9">
         <f t="shared" si="18"/>
         <v>44.9</v>
       </c>
-      <c r="O21" s="9">
+      <c r="Q21" s="9">
         <f t="shared" si="18"/>
         <v>48.700000000000045</v>
       </c>
-      <c r="P21" s="9">
+      <c r="R21" s="9">
         <f t="shared" si="18"/>
         <v>157.20000000000005</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="S21" s="9">
         <f t="shared" si="18"/>
         <v>501.90000000000009</v>
       </c>
-      <c r="R21" s="9">
+      <c r="T21" s="9">
         <f t="shared" si="18"/>
-        <v>654.63855999999987</v>
-      </c>
-      <c r="S21" s="9">
+        <v>579.59999999999991</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="18"/>
-        <v>734.54567039999995</v>
-      </c>
-      <c r="T21" s="9">
-        <f t="shared" ref="T21:AB21" si="19">T17-T18-T19-T20</f>
-        <v>793.92464292000011</v>
-      </c>
-      <c r="U21" s="9">
-        <f t="shared" si="19"/>
-        <v>838.44218384440023</v>
+        <v>660.58101999999997</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="19"/>
-        <v>876.8406987206281</v>
+        <f t="shared" ref="V21:AD21" si="19">V17-V18-V19-V20</f>
+        <v>711.61788500000023</v>
       </c>
       <c r="W21" s="9">
         <f t="shared" si="19"/>
-        <v>908.77045293031574</v>
+        <v>750.11845015000051</v>
       </c>
       <c r="X21" s="9">
         <f t="shared" si="19"/>
-        <v>940.2426602691811</v>
+        <v>785.57458104330055</v>
       </c>
       <c r="Y21" s="9">
         <f t="shared" si="19"/>
-        <v>959.45229720308805</v>
+        <v>815.36798869053655</v>
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="19"/>
-        <v>979.05827038752921</v>
+        <v>844.97107124361366</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="19"/>
-        <v>999.06887085286985</v>
+        <v>862.26811208323022</v>
       </c>
       <c r="AB21" s="9">
         <f t="shared" si="19"/>
-        <v>1019.4925663792455</v>
-      </c>
-    </row>
-    <row r="22" spans="1:147" x14ac:dyDescent="0.3">
+        <v>879.92302232208124</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="19"/>
+        <v>897.94331720562502</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="19"/>
+        <v>916.33667301995251</v>
+      </c>
+    </row>
+    <row r="22" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>30</v>
       </c>
@@ -2232,94 +2297,96 @@
         <v>2.5</v>
       </c>
       <c r="D22" s="2">
-        <f>O22-C22</f>
+        <f>Q22-C22</f>
         <v>2.2999999999999998</v>
       </c>
       <c r="E22" s="2">
         <v>3.7</v>
       </c>
       <c r="F22" s="2">
-        <f>P22-E22</f>
+        <f>R22-E22</f>
         <v>6.9999999999999991</v>
       </c>
       <c r="G22" s="2">
         <v>9.3000000000000007</v>
       </c>
       <c r="H22" s="2">
-        <f>Q22-G22</f>
+        <f>S22-G22</f>
         <v>11.2</v>
       </c>
       <c r="I22" s="2">
         <v>9.4</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="14">
         <f>H22*1.05</f>
         <v>11.76</v>
       </c>
-      <c r="L22" s="2">
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="N22" s="2">
         <v>2.1</v>
       </c>
-      <c r="M22" s="2">
+      <c r="O22" s="2">
         <v>3.2</v>
       </c>
-      <c r="N22" s="2">
+      <c r="P22" s="2">
         <v>3.8</v>
       </c>
-      <c r="O22" s="2">
+      <c r="Q22" s="2">
         <v>4.8</v>
       </c>
-      <c r="P22" s="2">
+      <c r="R22" s="2">
         <v>10.7</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="S22" s="2">
         <v>20.5</v>
       </c>
-      <c r="R22" s="2">
-        <f>SUM(I22:J22)</f>
-        <v>21.16</v>
-      </c>
-      <c r="S22" s="2">
-        <f>R22*1.03</f>
-        <v>21.794800000000002</v>
-      </c>
       <c r="T22" s="2">
-        <f t="shared" ref="T22:AB22" si="20">S22*1.03</f>
-        <v>22.448644000000002</v>
+        <f>-0.7+15.5</f>
+        <v>14.8</v>
       </c>
       <c r="U22" s="2">
-        <f t="shared" si="20"/>
-        <v>23.122103320000001</v>
+        <f>T22*1.03</f>
+        <v>15.244000000000002</v>
       </c>
       <c r="V22" s="2">
-        <f t="shared" si="20"/>
-        <v>23.815766419600003</v>
+        <f t="shared" ref="V22:AD22" si="20">U22*1.03</f>
+        <v>15.701320000000003</v>
       </c>
       <c r="W22" s="2">
         <f t="shared" si="20"/>
-        <v>24.530239412188003</v>
+        <v>16.172359600000004</v>
       </c>
       <c r="X22" s="2">
         <f t="shared" si="20"/>
-        <v>25.266146594553643</v>
+        <v>16.657530388000005</v>
       </c>
       <c r="Y22" s="2">
         <f t="shared" si="20"/>
-        <v>26.024130992390251</v>
+        <v>17.157256299640007</v>
       </c>
       <c r="Z22" s="2">
         <f t="shared" si="20"/>
-        <v>26.804854922161958</v>
+        <v>17.671973988629208</v>
       </c>
       <c r="AA22" s="2">
         <f t="shared" si="20"/>
-        <v>27.609000569826819</v>
+        <v>18.202133208288085</v>
       </c>
       <c r="AB22" s="2">
         <f t="shared" si="20"/>
-        <v>28.437270586921624</v>
-      </c>
-    </row>
-    <row r="23" spans="1:147" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>18.74819720453673</v>
+      </c>
+      <c r="AC22" s="2">
+        <f t="shared" si="20"/>
+        <v>19.310643120672832</v>
+      </c>
+      <c r="AD22" s="2">
+        <f t="shared" si="20"/>
+        <v>19.889962414293016</v>
+      </c>
+    </row>
+    <row r="23" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23"/>
       <c r="B23" s="8" t="s">
         <v>31</v>
@@ -2352,80 +2419,82 @@
         <f t="shared" ref="I23:J23" si="22">I21-I22</f>
         <v>292.49999999999989</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="15">
         <f t="shared" si="22"/>
         <v>340.97856000000007</v>
       </c>
-      <c r="L23" s="9">
-        <f t="shared" ref="L23:S23" si="23">L21-L22</f>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="N23" s="9">
+        <f t="shared" ref="N23:U23" si="23">N21-N22</f>
         <v>10.100000000000007</v>
       </c>
-      <c r="M23" s="9">
+      <c r="O23" s="9">
         <f t="shared" si="23"/>
         <v>20.000000000000014</v>
       </c>
-      <c r="N23" s="9">
+      <c r="P23" s="9">
         <f t="shared" si="23"/>
         <v>41.1</v>
       </c>
-      <c r="O23" s="9">
+      <c r="Q23" s="9">
         <f t="shared" si="23"/>
         <v>43.900000000000048</v>
       </c>
-      <c r="P23" s="9">
+      <c r="R23" s="9">
         <f t="shared" si="23"/>
         <v>146.50000000000006</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="S23" s="9">
         <f t="shared" si="23"/>
         <v>481.40000000000009</v>
       </c>
-      <c r="R23" s="9">
+      <c r="T23" s="9">
         <f t="shared" si="23"/>
-        <v>633.4785599999999</v>
-      </c>
-      <c r="S23" s="9">
+        <v>564.79999999999995</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="23"/>
-        <v>712.75087039999994</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" ref="T23:AB23" si="24">T21-T22</f>
-        <v>771.47599892000017</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="24"/>
-        <v>815.32008052440028</v>
+        <v>645.33701999999994</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="24"/>
-        <v>853.02493230102812</v>
+        <f t="shared" ref="V23:AD23" si="24">V21-V22</f>
+        <v>695.91656500000022</v>
       </c>
       <c r="W23" s="9">
         <f t="shared" si="24"/>
-        <v>884.24021351812769</v>
+        <v>733.94609055000046</v>
       </c>
       <c r="X23" s="9">
         <f t="shared" si="24"/>
-        <v>914.97651367462743</v>
+        <v>768.9170506553005</v>
       </c>
       <c r="Y23" s="9">
         <f t="shared" si="24"/>
-        <v>933.42816621069778</v>
+        <v>798.21073239089651</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" si="24"/>
-        <v>952.2534154653672</v>
+        <v>827.29909725498442</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="24"/>
-        <v>971.45987028304307</v>
+        <v>844.06597887494218</v>
       </c>
       <c r="AB23" s="9">
         <f t="shared" si="24"/>
-        <v>991.05529579232393</v>
-      </c>
-    </row>
-    <row r="24" spans="1:147" x14ac:dyDescent="0.3">
+        <v>861.17482511754451</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="24"/>
+        <v>878.63267408495221</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="24"/>
+        <v>896.44671060565952</v>
+      </c>
+    </row>
+    <row r="24" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>32</v>
       </c>
@@ -2433,94 +2502,95 @@
         <v>6.1</v>
       </c>
       <c r="D24" s="2">
-        <f>O24-C24</f>
+        <f>Q24-C24</f>
         <v>4.9000000000000004</v>
       </c>
       <c r="E24" s="2">
         <v>14</v>
       </c>
       <c r="F24" s="2">
-        <f>P24-E24</f>
+        <f>R24-E24</f>
         <v>18.5</v>
       </c>
       <c r="G24" s="2">
         <v>53.7</v>
       </c>
       <c r="H24" s="2">
-        <f>Q24-G24</f>
+        <f>S24-G24</f>
         <v>73.099999999999994</v>
       </c>
       <c r="I24" s="2">
         <v>75.2</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="14">
         <f>J23*0.25</f>
         <v>85.244640000000018</v>
       </c>
-      <c r="L24" s="2">
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="N24" s="2">
         <v>-0.2</v>
       </c>
-      <c r="M24" s="2">
+      <c r="O24" s="2">
         <v>5.4</v>
       </c>
-      <c r="N24" s="2">
+      <c r="P24" s="2">
         <v>10.199999999999999</v>
       </c>
-      <c r="O24" s="2">
+      <c r="Q24" s="2">
         <v>11</v>
       </c>
-      <c r="P24" s="2">
+      <c r="R24" s="2">
         <v>32.5</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="S24" s="2">
         <v>126.8</v>
       </c>
-      <c r="R24" s="2">
-        <f>SUM(I24:J24)</f>
-        <v>160.44464000000002</v>
-      </c>
-      <c r="S24" s="2">
-        <f>S23*0.25</f>
-        <v>178.18771759999998</v>
-      </c>
       <c r="T24" s="2">
-        <f t="shared" ref="T24:AB24" si="25">T23*0.25</f>
-        <v>192.86899973000004</v>
+        <v>148.1</v>
       </c>
       <c r="U24" s="2">
-        <f t="shared" si="25"/>
-        <v>203.83002013110007</v>
+        <f>U23*0.25</f>
+        <v>161.33425499999998</v>
       </c>
       <c r="V24" s="2">
-        <f t="shared" si="25"/>
-        <v>213.25623307525703</v>
+        <f t="shared" ref="V24:AD24" si="25">V23*0.25</f>
+        <v>173.97914125000005</v>
       </c>
       <c r="W24" s="2">
         <f t="shared" si="25"/>
-        <v>221.06005337953192</v>
+        <v>183.48652263750012</v>
       </c>
       <c r="X24" s="2">
         <f t="shared" si="25"/>
-        <v>228.74412841865686</v>
+        <v>192.22926266382512</v>
       </c>
       <c r="Y24" s="2">
         <f t="shared" si="25"/>
-        <v>233.35704155267445</v>
+        <v>199.55268309772413</v>
       </c>
       <c r="Z24" s="2">
         <f t="shared" si="25"/>
-        <v>238.0633538663418</v>
+        <v>206.8247743137461</v>
       </c>
       <c r="AA24" s="2">
         <f t="shared" si="25"/>
-        <v>242.86496757076077</v>
+        <v>211.01649471873554</v>
       </c>
       <c r="AB24" s="2">
         <f t="shared" si="25"/>
-        <v>247.76382394808098</v>
-      </c>
-    </row>
-    <row r="25" spans="1:147" s="8" customFormat="1" x14ac:dyDescent="0.3">
+        <v>215.29370627938613</v>
+      </c>
+      <c r="AC24" s="2">
+        <f t="shared" si="25"/>
+        <v>219.65816852123805</v>
+      </c>
+      <c r="AD24" s="2">
+        <f t="shared" si="25"/>
+        <v>224.11167765141488</v>
+      </c>
+    </row>
+    <row r="25" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25"/>
       <c r="B25" s="8" t="s">
         <v>33</v>
@@ -2553,556 +2623,558 @@
         <f t="shared" ref="I25:J25" si="27">I23-I24</f>
         <v>217.2999999999999</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="15">
         <f t="shared" si="27"/>
         <v>255.73392000000007</v>
       </c>
-      <c r="L25" s="9">
-        <f t="shared" ref="L25:S25" si="28">L23-L24</f>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="N25" s="9">
+        <f t="shared" ref="N25:U25" si="28">N23-N24</f>
         <v>10.300000000000006</v>
       </c>
-      <c r="M25" s="9">
+      <c r="O25" s="9">
         <f t="shared" si="28"/>
         <v>14.600000000000014</v>
       </c>
-      <c r="N25" s="9">
+      <c r="P25" s="9">
         <f t="shared" si="28"/>
         <v>30.900000000000002</v>
       </c>
-      <c r="O25" s="9">
+      <c r="Q25" s="9">
         <f t="shared" si="28"/>
         <v>32.900000000000048</v>
       </c>
-      <c r="P25" s="9">
+      <c r="R25" s="9">
         <f t="shared" si="28"/>
         <v>114.00000000000006</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="S25" s="9">
         <f t="shared" si="28"/>
         <v>354.60000000000008</v>
       </c>
-      <c r="R25" s="9">
+      <c r="T25" s="9">
         <f t="shared" si="28"/>
-        <v>473.03391999999985</v>
-      </c>
-      <c r="S25" s="9">
+        <v>416.69999999999993</v>
+      </c>
+      <c r="U25" s="9">
         <f t="shared" si="28"/>
-        <v>534.5631527999999</v>
-      </c>
-      <c r="T25" s="9">
-        <f t="shared" ref="T25:AB25" si="29">T23-T24</f>
-        <v>578.60699919000012</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="29"/>
-        <v>611.49006039330015</v>
+        <v>484.00276499999995</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="29"/>
-        <v>639.76869922577112</v>
+        <f t="shared" ref="V25:AD25" si="29">V23-V24</f>
+        <v>521.93742375000011</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" si="29"/>
-        <v>663.18016013859574</v>
+        <v>550.45956791250035</v>
       </c>
       <c r="X25" s="9">
         <f t="shared" si="29"/>
-        <v>686.2323852559706</v>
+        <v>576.68778799147537</v>
       </c>
       <c r="Y25" s="9">
         <f t="shared" si="29"/>
-        <v>700.07112465802334</v>
+        <v>598.65804929317233</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" si="29"/>
-        <v>714.1900615990254</v>
+        <v>620.47432294123837</v>
       </c>
       <c r="AA25" s="9">
         <f t="shared" si="29"/>
-        <v>728.59490271228231</v>
+        <v>633.04948415620663</v>
       </c>
       <c r="AB25" s="9">
         <f t="shared" si="29"/>
-        <v>743.29147184424301</v>
-      </c>
-      <c r="AC25" s="8">
-        <f>AB25+(AB25*$AE$35)</f>
-        <v>735.85855712580053</v>
-      </c>
-      <c r="AD25" s="8">
-        <f t="shared" ref="AD25:CO25" si="30">AC25+(AC25*$AE$35)</f>
-        <v>728.49997155454253</v>
+        <v>645.88111883815839</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="29"/>
+        <v>658.97450556371416</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="29"/>
+        <v>672.33503295424464</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="30"/>
-        <v>721.21497183899714</v>
+        <f>AD25+(AD25*$AG$35)</f>
+        <v>665.61168262470221</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="30"/>
-        <v>714.00282212060722</v>
+        <f t="shared" ref="AF25:CQ25" si="30">AE25+(AE25*$AG$35)</f>
+        <v>658.95556579845515</v>
       </c>
       <c r="AG25" s="8">
         <f t="shared" si="30"/>
-        <v>706.86279389940114</v>
+        <v>652.36601014047062</v>
       </c>
       <c r="AH25" s="8">
         <f t="shared" si="30"/>
-        <v>699.7941659604071</v>
+        <v>645.84235003906588</v>
       </c>
       <c r="AI25" s="8">
         <f t="shared" si="30"/>
-        <v>692.79622430080303</v>
+        <v>639.38392653867527</v>
       </c>
       <c r="AJ25" s="8">
         <f t="shared" si="30"/>
-        <v>685.86826205779505</v>
+        <v>632.99008727328851</v>
       </c>
       <c r="AK25" s="8">
         <f t="shared" si="30"/>
-        <v>679.0095794372171</v>
+        <v>626.66018640055563</v>
       </c>
       <c r="AL25" s="8">
         <f t="shared" si="30"/>
-        <v>672.21948364284492</v>
+        <v>620.39358453655007</v>
       </c>
       <c r="AM25" s="8">
         <f t="shared" si="30"/>
-        <v>665.49728880641646</v>
+        <v>614.18964869118452</v>
       </c>
       <c r="AN25" s="8">
         <f t="shared" si="30"/>
-        <v>658.84231591835226</v>
+        <v>608.04775220427268</v>
       </c>
       <c r="AO25" s="8">
         <f t="shared" si="30"/>
-        <v>652.25389275916871</v>
+        <v>601.96727468222991</v>
       </c>
       <c r="AP25" s="8">
         <f t="shared" si="30"/>
-        <v>645.73135383157705</v>
+        <v>595.94760193540765</v>
       </c>
       <c r="AQ25" s="8">
         <f t="shared" si="30"/>
-        <v>639.27404029326124</v>
+        <v>589.9881259160536</v>
       </c>
       <c r="AR25" s="8">
         <f t="shared" si="30"/>
-        <v>632.88129989032859</v>
+        <v>584.08824465689304</v>
       </c>
       <c r="AS25" s="8">
         <f t="shared" si="30"/>
-        <v>626.55248689142536</v>
+        <v>578.24736221032413</v>
       </c>
       <c r="AT25" s="8">
         <f t="shared" si="30"/>
-        <v>620.28696202251115</v>
+        <v>572.4648885882209</v>
       </c>
       <c r="AU25" s="8">
         <f t="shared" si="30"/>
-        <v>614.08409240228605</v>
+        <v>566.74023970233873</v>
       </c>
       <c r="AV25" s="8">
         <f t="shared" si="30"/>
-        <v>607.94325147826316</v>
+        <v>561.07283730531537</v>
       </c>
       <c r="AW25" s="8">
         <f t="shared" si="30"/>
-        <v>601.86381896348053</v>
+        <v>555.46210893226225</v>
       </c>
       <c r="AX25" s="8">
         <f t="shared" si="30"/>
-        <v>595.84518077384575</v>
+        <v>549.90748784293964</v>
       </c>
       <c r="AY25" s="8">
         <f t="shared" si="30"/>
-        <v>589.88672896610728</v>
+        <v>544.40841296451026</v>
       </c>
       <c r="AZ25" s="8">
         <f t="shared" si="30"/>
-        <v>583.98786167644619</v>
+        <v>538.96432883486511</v>
       </c>
       <c r="BA25" s="8">
         <f t="shared" si="30"/>
-        <v>578.14798305968168</v>
+        <v>533.57468554651643</v>
       </c>
       <c r="BB25" s="8">
         <f t="shared" si="30"/>
-        <v>572.36650322908486</v>
+        <v>528.23893869105132</v>
       </c>
       <c r="BC25" s="8">
         <f t="shared" si="30"/>
-        <v>566.64283819679406</v>
+        <v>522.95654930414082</v>
       </c>
       <c r="BD25" s="8">
         <f t="shared" si="30"/>
-        <v>560.97640981482607</v>
+        <v>517.72698381109944</v>
       </c>
       <c r="BE25" s="8">
         <f t="shared" si="30"/>
-        <v>555.36664571667779</v>
+        <v>512.54971397298846</v>
       </c>
       <c r="BF25" s="8">
         <f t="shared" si="30"/>
-        <v>549.81297925951105</v>
+        <v>507.42421683325858</v>
       </c>
       <c r="BG25" s="8">
         <f t="shared" si="30"/>
-        <v>544.31484946691592</v>
+        <v>502.34997466492598</v>
       </c>
       <c r="BH25" s="8">
         <f t="shared" si="30"/>
-        <v>538.8717009722468</v>
+        <v>497.32647491827674</v>
       </c>
       <c r="BI25" s="8">
         <f t="shared" si="30"/>
-        <v>533.48298396252437</v>
+        <v>492.35321016909398</v>
       </c>
       <c r="BJ25" s="8">
         <f t="shared" si="30"/>
-        <v>528.14815412289909</v>
+        <v>487.42967806740302</v>
       </c>
       <c r="BK25" s="8">
         <f t="shared" si="30"/>
-        <v>522.86667258167006</v>
+        <v>482.55538128672896</v>
       </c>
       <c r="BL25" s="8">
         <f t="shared" si="30"/>
-        <v>517.63800585585341</v>
+        <v>477.72982747386169</v>
       </c>
       <c r="BM25" s="8">
         <f t="shared" si="30"/>
-        <v>512.46162579729491</v>
+        <v>472.95252919912309</v>
       </c>
       <c r="BN25" s="8">
         <f t="shared" si="30"/>
-        <v>507.33700953932197</v>
+        <v>468.22300390713184</v>
       </c>
       <c r="BO25" s="8">
         <f t="shared" si="30"/>
-        <v>502.26363944392875</v>
+        <v>463.54077386806051</v>
       </c>
       <c r="BP25" s="8">
         <f t="shared" si="30"/>
-        <v>497.24100304948945</v>
+        <v>458.9053661293799</v>
       </c>
       <c r="BQ25" s="8">
         <f t="shared" si="30"/>
-        <v>492.26859301899458</v>
+        <v>454.3163124680861</v>
       </c>
       <c r="BR25" s="8">
         <f t="shared" si="30"/>
-        <v>487.34590708880461</v>
+        <v>449.77314934340524</v>
       </c>
       <c r="BS25" s="8">
         <f t="shared" si="30"/>
-        <v>482.47244801791658</v>
+        <v>445.27541784997118</v>
       </c>
       <c r="BT25" s="8">
         <f t="shared" si="30"/>
-        <v>477.64772353773742</v>
+        <v>440.82266367147145</v>
       </c>
       <c r="BU25" s="8">
         <f t="shared" si="30"/>
-        <v>472.87124630236002</v>
+        <v>436.41443703475676</v>
       </c>
       <c r="BV25" s="8">
         <f t="shared" si="30"/>
-        <v>468.14253383933641</v>
+        <v>432.0502926644092</v>
       </c>
       <c r="BW25" s="8">
         <f t="shared" si="30"/>
-        <v>463.46110850094306</v>
+        <v>427.72978973776509</v>
       </c>
       <c r="BX25" s="8">
         <f t="shared" si="30"/>
-        <v>458.8264974159336</v>
+        <v>423.45249184038744</v>
       </c>
       <c r="BY25" s="8">
         <f t="shared" si="30"/>
-        <v>454.23823244177424</v>
+        <v>419.21796692198359</v>
       </c>
       <c r="BZ25" s="8">
         <f t="shared" si="30"/>
-        <v>449.69585011735649</v>
+        <v>415.02578725276373</v>
       </c>
       <c r="CA25" s="8">
         <f t="shared" si="30"/>
-        <v>445.19889161618295</v>
+        <v>410.87552938023612</v>
       </c>
       <c r="CB25" s="8">
         <f t="shared" si="30"/>
-        <v>440.74690270002111</v>
+        <v>406.76677408643377</v>
       </c>
       <c r="CC25" s="8">
         <f t="shared" si="30"/>
-        <v>436.33943367302089</v>
+        <v>402.69910634556942</v>
       </c>
       <c r="CD25" s="8">
         <f t="shared" si="30"/>
-        <v>431.97603933629068</v>
+        <v>398.67211528211374</v>
       </c>
       <c r="CE25" s="8">
         <f t="shared" si="30"/>
-        <v>427.65627894292777</v>
+        <v>394.6853941292926</v>
       </c>
       <c r="CF25" s="8">
         <f t="shared" si="30"/>
-        <v>423.37971615349852</v>
+        <v>390.73854018799966</v>
       </c>
       <c r="CG25" s="8">
         <f t="shared" si="30"/>
-        <v>419.14591899196353</v>
+        <v>386.83115478611967</v>
       </c>
       <c r="CH25" s="8">
         <f t="shared" si="30"/>
-        <v>414.95445980204391</v>
+        <v>382.96284323825847</v>
       </c>
       <c r="CI25" s="8">
         <f t="shared" si="30"/>
-        <v>410.80491520402347</v>
+        <v>379.13321480587587</v>
       </c>
       <c r="CJ25" s="8">
         <f t="shared" si="30"/>
-        <v>406.69686605198325</v>
+        <v>375.34188265781711</v>
       </c>
       <c r="CK25" s="8">
         <f t="shared" si="30"/>
-        <v>402.62989739146343</v>
+        <v>371.58846383123893</v>
       </c>
       <c r="CL25" s="8">
         <f t="shared" si="30"/>
-        <v>398.60359841754882</v>
+        <v>367.87257919292654</v>
       </c>
       <c r="CM25" s="8">
         <f t="shared" si="30"/>
-        <v>394.61756243337334</v>
+        <v>364.19385340099728</v>
       </c>
       <c r="CN25" s="8">
         <f t="shared" si="30"/>
-        <v>390.67138680903963</v>
+        <v>360.55191486698732</v>
       </c>
       <c r="CO25" s="8">
         <f t="shared" si="30"/>
-        <v>386.76467294094925</v>
+        <v>356.94639571831743</v>
       </c>
       <c r="CP25" s="8">
-        <f t="shared" ref="CP25:EQ25" si="31">CO25+(CO25*$AE$35)</f>
-        <v>382.89702621153975</v>
+        <f t="shared" si="30"/>
+        <v>353.37693176113424</v>
       </c>
       <c r="CQ25" s="8">
-        <f t="shared" si="31"/>
-        <v>379.06805594942438</v>
+        <f t="shared" si="30"/>
+        <v>349.84316244352289</v>
       </c>
       <c r="CR25" s="8">
-        <f t="shared" si="31"/>
-        <v>375.27737538993011</v>
+        <f t="shared" ref="CR25:ES25" si="31">CQ25+(CQ25*$AG$35)</f>
+        <v>346.34473081908766</v>
       </c>
       <c r="CS25" s="8">
         <f t="shared" si="31"/>
-        <v>371.52460163603081</v>
+        <v>342.88128351089676</v>
       </c>
       <c r="CT25" s="8">
         <f t="shared" si="31"/>
-        <v>367.8093556196705</v>
+        <v>339.45247067578782</v>
       </c>
       <c r="CU25" s="8">
         <f t="shared" si="31"/>
-        <v>364.1312620634738</v>
+        <v>336.05794596902996</v>
       </c>
       <c r="CV25" s="8">
         <f t="shared" si="31"/>
-        <v>360.48994944283908</v>
+        <v>332.69736650933964</v>
       </c>
       <c r="CW25" s="8">
         <f t="shared" si="31"/>
-        <v>356.88504994841071</v>
+        <v>329.37039284424623</v>
       </c>
       <c r="CX25" s="8">
         <f t="shared" si="31"/>
-        <v>353.31619944892662</v>
+        <v>326.07668891580374</v>
       </c>
       <c r="CY25" s="8">
         <f t="shared" si="31"/>
-        <v>349.78303745443736</v>
+        <v>322.81592202664569</v>
       </c>
       <c r="CZ25" s="8">
         <f t="shared" si="31"/>
-        <v>346.28520707989298</v>
+        <v>319.58776280637926</v>
       </c>
       <c r="DA25" s="8">
         <f t="shared" si="31"/>
-        <v>342.82235500909405</v>
+        <v>316.39188517831548</v>
       </c>
       <c r="DB25" s="8">
         <f t="shared" si="31"/>
-        <v>339.39413145900312</v>
+        <v>313.22796632653234</v>
       </c>
       <c r="DC25" s="8">
         <f t="shared" si="31"/>
-        <v>336.00019014441307</v>
+        <v>310.09568666326703</v>
       </c>
       <c r="DD25" s="8">
         <f t="shared" si="31"/>
-        <v>332.64018824296892</v>
+        <v>306.99472979663437</v>
       </c>
       <c r="DE25" s="8">
         <f t="shared" si="31"/>
-        <v>329.31378636053921</v>
+        <v>303.92478249866804</v>
       </c>
       <c r="DF25" s="8">
         <f t="shared" si="31"/>
-        <v>326.0206484969338</v>
+        <v>300.88553467368138</v>
       </c>
       <c r="DG25" s="8">
         <f t="shared" si="31"/>
-        <v>322.76044201196447</v>
+        <v>297.87667932694455</v>
       </c>
       <c r="DH25" s="8">
         <f t="shared" si="31"/>
-        <v>319.53283759184484</v>
+        <v>294.89791253367508</v>
       </c>
       <c r="DI25" s="8">
         <f t="shared" si="31"/>
-        <v>316.33750921592639</v>
+        <v>291.94893340833835</v>
       </c>
       <c r="DJ25" s="8">
         <f t="shared" si="31"/>
-        <v>313.17413412376715</v>
+        <v>289.02944407425497</v>
       </c>
       <c r="DK25" s="8">
         <f t="shared" si="31"/>
-        <v>310.04239278252948</v>
+        <v>286.13914963351243</v>
       </c>
       <c r="DL25" s="8">
         <f t="shared" si="31"/>
-        <v>306.94196885470416</v>
+        <v>283.27775813717733</v>
       </c>
       <c r="DM25" s="8">
         <f t="shared" si="31"/>
-        <v>303.87254916615711</v>
+        <v>280.44498055580556</v>
       </c>
       <c r="DN25" s="8">
         <f t="shared" si="31"/>
-        <v>300.83382367449553</v>
+        <v>277.64053075024748</v>
       </c>
       <c r="DO25" s="8">
         <f t="shared" si="31"/>
-        <v>297.82548543775056</v>
+        <v>274.86412544274498</v>
       </c>
       <c r="DP25" s="8">
         <f t="shared" si="31"/>
-        <v>294.84723058337306</v>
+        <v>272.11548418831751</v>
       </c>
       <c r="DQ25" s="8">
         <f t="shared" si="31"/>
-        <v>291.89875827753934</v>
+        <v>269.39432934643435</v>
       </c>
       <c r="DR25" s="8">
         <f t="shared" si="31"/>
-        <v>288.97977069476394</v>
+        <v>266.70038605296998</v>
       </c>
       <c r="DS25" s="8">
         <f t="shared" si="31"/>
-        <v>286.08997298781628</v>
+        <v>264.03338219244029</v>
       </c>
       <c r="DT25" s="8">
         <f t="shared" si="31"/>
-        <v>283.22907325793813</v>
+        <v>261.39304837051588</v>
       </c>
       <c r="DU25" s="8">
         <f t="shared" si="31"/>
-        <v>280.39678252535873</v>
+        <v>258.77911788681075</v>
       </c>
       <c r="DV25" s="8">
         <f t="shared" si="31"/>
-        <v>277.59281470010512</v>
+        <v>256.19132670794266</v>
       </c>
       <c r="DW25" s="8">
         <f t="shared" si="31"/>
-        <v>274.8168865531041</v>
+        <v>253.62941344086323</v>
       </c>
       <c r="DX25" s="8">
         <f t="shared" si="31"/>
-        <v>272.06871768757304</v>
+        <v>251.09311930645461</v>
       </c>
       <c r="DY25" s="8">
         <f t="shared" si="31"/>
-        <v>269.3480305106973</v>
+        <v>248.58218811339006</v>
       </c>
       <c r="DZ25" s="8">
         <f t="shared" si="31"/>
-        <v>266.65455020559034</v>
+        <v>246.09636623225617</v>
       </c>
       <c r="EA25" s="8">
         <f t="shared" si="31"/>
-        <v>263.98800470353444</v>
+        <v>243.6354025699336</v>
       </c>
       <c r="EB25" s="8">
         <f t="shared" si="31"/>
-        <v>261.34812465649912</v>
+        <v>241.19904854423427</v>
       </c>
       <c r="EC25" s="8">
         <f t="shared" si="31"/>
-        <v>258.73464340993411</v>
+        <v>238.78705805879193</v>
       </c>
       <c r="ED25" s="8">
         <f t="shared" si="31"/>
-        <v>256.14729697583476</v>
+        <v>236.399187478204</v>
       </c>
       <c r="EE25" s="8">
         <f t="shared" si="31"/>
-        <v>253.58582400607642</v>
+        <v>234.03519560342195</v>
       </c>
       <c r="EF25" s="8">
         <f t="shared" si="31"/>
-        <v>251.04996576601565</v>
+        <v>231.69484364738773</v>
       </c>
       <c r="EG25" s="8">
         <f t="shared" si="31"/>
-        <v>248.5394661083555</v>
+        <v>229.37789521091386</v>
       </c>
       <c r="EH25" s="8">
         <f t="shared" si="31"/>
-        <v>246.05407144727195</v>
+        <v>227.08411625880473</v>
       </c>
       <c r="EI25" s="8">
         <f t="shared" si="31"/>
-        <v>243.59353073279922</v>
+        <v>224.81327509621667</v>
       </c>
       <c r="EJ25" s="8">
         <f t="shared" si="31"/>
-        <v>241.15759542547124</v>
+        <v>222.56514234525451</v>
       </c>
       <c r="EK25" s="8">
         <f t="shared" si="31"/>
-        <v>238.74601947121653</v>
+        <v>220.33949092180197</v>
       </c>
       <c r="EL25" s="8">
         <f t="shared" si="31"/>
-        <v>236.35855927650437</v>
+        <v>218.13609601258395</v>
       </c>
       <c r="EM25" s="8">
         <f t="shared" si="31"/>
-        <v>233.99497368373932</v>
+        <v>215.95473505245812</v>
       </c>
       <c r="EN25" s="8">
         <f t="shared" si="31"/>
-        <v>231.65502394690193</v>
+        <v>213.79518770193354</v>
       </c>
       <c r="EO25" s="8">
         <f t="shared" si="31"/>
-        <v>229.33847370743291</v>
+        <v>211.65723582491421</v>
       </c>
       <c r="EP25" s="8">
         <f t="shared" si="31"/>
-        <v>227.04508897035859</v>
+        <v>209.54066346666508</v>
       </c>
       <c r="EQ25" s="8">
         <f t="shared" si="31"/>
-        <v>224.774638080655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:147" x14ac:dyDescent="0.3">
+        <v>207.44525683199842</v>
+      </c>
+      <c r="ER25" s="8">
+        <f t="shared" si="31"/>
+        <v>205.37080426367842</v>
+      </c>
+      <c r="ES25" s="8">
+        <f t="shared" si="31"/>
+        <v>203.31709622104165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>1</v>
       </c>
@@ -3134,18 +3206,13 @@
         <v>1029.0999999999999</v>
       </c>
       <c r="J26" s="2">
-        <v>1029.0999999999999</v>
-      </c>
-      <c r="L26" s="2">
-        <f t="shared" ref="L26:Q26" si="33">1423.7</f>
-        <v>1423.7</v>
-      </c>
-      <c r="M26" s="2">
-        <f t="shared" si="33"/>
-        <v>1423.7</v>
-      </c>
+        <f>1032.2</f>
+        <v>1032.2</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
       <c r="N26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="N26:S26" si="33">1423.7</f>
         <v>1423.7</v>
       </c>
       <c r="O26" s="2">
@@ -3161,145 +3228,166 @@
         <v>1423.7</v>
       </c>
       <c r="R26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="33"/>
+        <v>1423.7</v>
       </c>
       <c r="S26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="33"/>
+        <v>1423.7</v>
       </c>
       <c r="T26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" ref="T26:AD26" si="34">1032.2</f>
+        <v>1032.2</v>
       </c>
       <c r="U26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="V26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="W26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="X26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="Y26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="Z26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="AA26" s="2">
-        <v>1029.0999999999999</v>
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
       </c>
       <c r="AB26" s="2">
-        <v>1029.0999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:147" x14ac:dyDescent="0.3">
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
+      </c>
+      <c r="AC26" s="2">
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
+      </c>
+      <c r="AD26" s="2">
+        <f t="shared" si="34"/>
+        <v>1032.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:H27" si="34">C25/C26</f>
+        <f t="shared" ref="C27:H27" si="35">C25/C26</f>
         <v>8.9204186275198653E-3</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.4188382383929166E-2</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.6199339748542508E-2</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.3873709348879667E-2</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>9.8756760553487366E-2</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.15031256584954697</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" ref="I27:J27" si="35">I25/I26</f>
+        <f t="shared" ref="I27:J27" si="36">I25/I26</f>
         <v>0.2111553784860557</v>
       </c>
-      <c r="J27" s="7">
-        <f t="shared" si="35"/>
-        <v>0.24850249732776222</v>
-      </c>
-      <c r="L27" s="7">
-        <f t="shared" ref="L27:S27" si="36">L25/L26</f>
+      <c r="J27" s="16">
+        <f t="shared" si="36"/>
+        <v>0.24775617128463481</v>
+      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="N27" s="7">
+        <f t="shared" ref="N27:U27" si="37">N25/N26</f>
         <v>7.2346702254688531E-3</v>
       </c>
-      <c r="M27" s="7">
-        <f t="shared" si="36"/>
+      <c r="O27" s="7">
+        <f t="shared" si="37"/>
         <v>1.0254969445810223E-2</v>
       </c>
-      <c r="N27" s="7">
-        <f t="shared" si="36"/>
+      <c r="P27" s="7">
+        <f t="shared" si="37"/>
         <v>2.1704010676406548E-2</v>
       </c>
-      <c r="O27" s="7">
-        <f t="shared" si="36"/>
+      <c r="Q27" s="7">
+        <f t="shared" si="37"/>
         <v>2.3108801011449076E-2</v>
       </c>
-      <c r="P27" s="7">
-        <f t="shared" si="36"/>
+      <c r="R27" s="7">
+        <f t="shared" si="37"/>
         <v>8.0073049097422244E-2</v>
       </c>
-      <c r="Q27" s="7">
-        <f t="shared" si="36"/>
+      <c r="S27" s="7">
+        <f t="shared" si="37"/>
         <v>0.24906932640303439</v>
       </c>
-      <c r="R27" s="7">
-        <f t="shared" si="36"/>
-        <v>0.45965787581381778</v>
-      </c>
-      <c r="S27" s="7">
-        <f t="shared" si="36"/>
-        <v>0.51944723816927407</v>
-      </c>
       <c r="T27" s="7">
-        <f t="shared" ref="T27:AB27" si="37">T25/T26</f>
-        <v>0.56224565075308541</v>
+        <f t="shared" si="37"/>
+        <v>0.40370083317186584</v>
       </c>
       <c r="U27" s="7">
         <f t="shared" si="37"/>
-        <v>0.59419887318365583</v>
+        <v>0.46890405444681255</v>
       </c>
       <c r="V27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.62167787311803635</v>
+        <f t="shared" ref="V27:AD27" si="38">V25/V26</f>
+        <v>0.5056553223696959</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.64442732498163036</v>
+        <f t="shared" si="38"/>
+        <v>0.53328770384857616</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.6668276992089891</v>
+        <f t="shared" si="38"/>
+        <v>0.55869772136356843</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.68027511870374446</v>
+        <f t="shared" si="38"/>
+        <v>0.57998260927453238</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.69399481255371243</v>
+        <f t="shared" si="38"/>
+        <v>0.6011183132544452</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.7079923260249561</v>
+        <f t="shared" si="38"/>
+        <v>0.61330118596803584</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.72227331828223018</v>
-      </c>
-    </row>
-    <row r="29" spans="1:147" x14ac:dyDescent="0.3">
+        <f t="shared" si="38"/>
+        <v>0.62573253132935314</v>
+      </c>
+      <c r="AC27" s="7">
+        <f t="shared" si="38"/>
+        <v>0.63841746324715576</v>
+      </c>
+      <c r="AD27" s="7">
+        <f t="shared" si="38"/>
+        <v>0.65136120224205063</v>
+      </c>
+    </row>
+    <row r="29" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>57</v>
       </c>
@@ -3307,19 +3395,21 @@
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:J30" si="38">H3/F3-1</f>
+        <f t="shared" ref="H29:J30" si="39">H3/F3-1</f>
         <v>0.13734142305570862</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.12400212879191042</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2492725509214448E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>58</v>
       </c>
@@ -3327,19 +3417,21 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.15137872819358478</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>5.8015267175572482E-2</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.0000000000000027E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+    </row>
+    <row r="31" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>59</v>
       </c>
@@ -3347,19 +3439,21 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:J32" si="39">H6/F6-1</f>
+        <f t="shared" ref="H31:J32" si="40">H6/F6-1</f>
         <v>0.60364464692482933</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.55038759689922467</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.38920454545454519</v>
       </c>
-    </row>
-    <row r="32" spans="1:147" x14ac:dyDescent="0.3">
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+    </row>
+    <row r="32" spans="1:149" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>60</v>
       </c>
@@ -3367,22 +3461,26 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.58515283842794763</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.49196141479099675</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.35000000000000009</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.3">
       <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>35</v>
       </c>
@@ -3393,82 +3491,84 @@
         <v>0.55052672649239165</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" ref="F34:J34" si="40">F10/D10-1</f>
+        <f t="shared" ref="F34:J34" si="41">F10/D10-1</f>
         <v>0.4779314888010544</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.25364871665827882</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.2342322264319141</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.18807707747892422</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.11854098952690517</v>
       </c>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
       <c r="O34" s="10"/>
-      <c r="P34" s="10">
-        <f t="shared" ref="P34:AB34" si="41">P10/O10-1</f>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10">
+        <f t="shared" ref="R34:AD34" si="42">R10/Q10-1</f>
         <v>0.51116270762636185</v>
       </c>
-      <c r="Q34" s="10">
-        <f t="shared" si="41"/>
+      <c r="S34" s="10">
+        <f t="shared" si="42"/>
         <v>0.24335184966316037</v>
       </c>
-      <c r="R34" s="10">
-        <f t="shared" si="41"/>
-        <v>0.15147148288973389</v>
-      </c>
-      <c r="S34" s="10">
-        <f t="shared" si="41"/>
+      <c r="T34" s="10">
+        <f t="shared" si="42"/>
+        <v>0.15199619771863127</v>
+      </c>
+      <c r="U34" s="10">
+        <f t="shared" si="42"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="T34" s="10">
-        <f t="shared" si="41"/>
+      <c r="V34" s="10">
+        <f t="shared" si="42"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="U34" s="10">
-        <f t="shared" si="41"/>
+      <c r="W34" s="10">
+        <f t="shared" si="42"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="V34" s="10">
-        <f t="shared" si="41"/>
+      <c r="X34" s="10">
+        <f t="shared" si="42"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="W34" s="10">
-        <f t="shared" si="41"/>
+      <c r="Y34" s="10">
+        <f t="shared" si="42"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="X34" s="10">
-        <f t="shared" si="41"/>
+      <c r="Z34" s="10">
+        <f t="shared" si="42"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="Y34" s="10">
-        <f t="shared" si="41"/>
+      <c r="AA34" s="10">
+        <f t="shared" si="42"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="41"/>
+      <c r="AB34" s="10">
+        <f t="shared" si="42"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="41"/>
+      <c r="AC34" s="10">
+        <f t="shared" si="42"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB34" s="10">
-        <f t="shared" si="41"/>
+      <c r="AD34" s="10">
+        <f t="shared" si="42"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>36</v>
       </c>
@@ -3479,88 +3579,90 @@
         <v>-16.583333333333329</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" ref="F35:J35" si="42">F11/D11-1</f>
+        <f t="shared" ref="F35:J35" si="43">F11/D11-1</f>
         <v>-74.625</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>10.288770053475936</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.3268251273344656</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.42444339175746082</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
       <c r="O35" s="10"/>
-      <c r="P35" s="10">
-        <f t="shared" ref="P35:AB35" si="43">P11/O11-1</f>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10">
+        <f t="shared" ref="R35:AD35" si="44">R11/Q11-1</f>
         <v>-49.749999999999993</v>
       </c>
-      <c r="Q35" s="10">
-        <f t="shared" si="43"/>
+      <c r="S35" s="10">
+        <f t="shared" si="44"/>
         <v>2.5545787545787544</v>
       </c>
-      <c r="R35" s="10">
-        <f t="shared" si="43"/>
-        <v>0.34284418796372629</v>
-      </c>
-      <c r="S35" s="10">
-        <f t="shared" si="43"/>
+      <c r="T35" s="10">
+        <f t="shared" si="44"/>
+        <v>0.22485572959604272</v>
+      </c>
+      <c r="U35" s="10">
+        <f t="shared" si="44"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="T35" s="10">
-        <f t="shared" si="43"/>
+      <c r="V35" s="10">
+        <f t="shared" si="44"/>
         <v>0.1100000000000001</v>
       </c>
-      <c r="U35" s="10">
-        <f t="shared" si="43"/>
+      <c r="W35" s="10">
+        <f t="shared" si="44"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="V35" s="10">
-        <f t="shared" si="43"/>
+      <c r="X35" s="10">
+        <f t="shared" si="44"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="W35" s="10">
-        <f t="shared" si="43"/>
+      <c r="Y35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="X35" s="10">
-        <f t="shared" si="43"/>
+      <c r="Z35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y35" s="10">
-        <f t="shared" si="43"/>
+      <c r="AA35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z35" s="10">
-        <f t="shared" si="43"/>
+      <c r="AB35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA35" s="10">
-        <f t="shared" si="43"/>
+      <c r="AC35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB35" s="10">
-        <f t="shared" si="43"/>
+      <c r="AD35" s="10">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AF35" t="s">
         <v>44</v>
       </c>
-      <c r="AE35" s="10">
+      <c r="AG35" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="36" spans="2:31" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
         <v>37</v>
       </c>
@@ -3571,152 +3673,154 @@
         <v>0.63112504900039168</v>
       </c>
       <c r="F36" s="11">
-        <f t="shared" ref="F36:J36" si="44">F12/D12-1</f>
+        <f t="shared" ref="F36:J36" si="45">F12/D12-1</f>
         <v>0.87582781456953684</v>
       </c>
       <c r="G36" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.70463830809901462</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.46142983230361878</v>
       </c>
       <c r="I36" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.25842379811081351</v>
       </c>
       <c r="J36" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.17199661794902776</v>
       </c>
-      <c r="M36" s="11">
-        <f>M12/L12-1</f>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="O36" s="11">
+        <f>O12/N12-1</f>
         <v>0.70095559302979216</v>
       </c>
-      <c r="N36" s="11">
-        <f t="shared" ref="N36:AB36" si="45">N12/M12-1</f>
+      <c r="P36" s="11">
+        <f t="shared" ref="P36:AD36" si="46">P12/O12-1</f>
         <v>0.3912756113681426</v>
       </c>
-      <c r="O36" s="11">
-        <f t="shared" si="45"/>
+      <c r="Q36" s="11">
+        <f t="shared" si="46"/>
         <v>0.32327790973871728</v>
       </c>
-      <c r="P36" s="11">
-        <f t="shared" si="45"/>
+      <c r="R36" s="11">
+        <f t="shared" si="46"/>
         <v>0.76377670077185411</v>
       </c>
-      <c r="Q36" s="11">
-        <f t="shared" si="45"/>
+      <c r="S36" s="11">
+        <f t="shared" si="46"/>
         <v>0.56442092407897415</v>
       </c>
-      <c r="R36" s="11">
-        <f t="shared" si="45"/>
-        <v>0.21187613843351549</v>
-      </c>
-      <c r="S36" s="11">
-        <f t="shared" si="45"/>
-        <v>0.13049250199689078</v>
-      </c>
       <c r="T36" s="11">
-        <f t="shared" si="45"/>
-        <v>0.10355785266896533</v>
+        <f t="shared" si="46"/>
+        <v>0.17499349466562575</v>
       </c>
       <c r="U36" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
+        <v>0.12987099988927042</v>
+      </c>
+      <c r="V36" s="11">
+        <f t="shared" si="46"/>
+        <v>0.10334895159824242</v>
+      </c>
+      <c r="W36" s="11">
+        <f t="shared" si="46"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="V36" s="11">
-        <f t="shared" si="45"/>
-        <v>4.2842755904459073E-2</v>
-      </c>
-      <c r="W36" s="11">
-        <f t="shared" si="45"/>
-        <v>3.2930898376895446E-2</v>
-      </c>
       <c r="X36" s="11">
-        <f t="shared" si="45"/>
-        <v>2.650969698607275E-2</v>
+        <f t="shared" si="46"/>
+        <v>4.3261721473221382E-2</v>
       </c>
       <c r="Y36" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
+        <v>3.3347377039022019E-2</v>
+      </c>
+      <c r="Z36" s="11">
+        <f t="shared" si="46"/>
+        <v>2.6716653290570491E-2</v>
+      </c>
+      <c r="AA36" s="11">
+        <f t="shared" si="46"/>
+        <v>2.000000000000024E-2</v>
+      </c>
+      <c r="AB36" s="11">
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z36" s="11">
-        <f t="shared" si="45"/>
+      <c r="AC36" s="11">
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA36" s="11">
-        <f t="shared" si="45"/>
+      <c r="AD36" s="11">
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB36" s="11">
-        <f t="shared" si="45"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD36" t="s">
+      <c r="AF36" t="s">
         <v>45</v>
       </c>
-      <c r="AE36" s="10">
+      <c r="AG36" s="10">
         <v>0.09</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="10">
-        <f t="shared" ref="C37:E37" si="46">(C10-(C15+C14))/C10</f>
+        <f t="shared" ref="C37:E37" si="47">(C10-(C15+C14))/C10</f>
         <v>0.67811158798283266</v>
       </c>
       <c r="D37" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.6525032938076416</v>
       </c>
       <c r="E37" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.61323603422244588</v>
       </c>
       <c r="F37" s="10">
-        <f t="shared" ref="F37:I37" si="47">(F10-(F15+F14))/F10</f>
+        <f t="shared" ref="F37:I37" si="48">(F10-(F15+F14))/F10</f>
         <v>0.61600178292846008</v>
       </c>
       <c r="G37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.66459253311922928</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.72408811845431564</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.7340767021456327</v>
       </c>
       <c r="J37" s="10">
         <f>(J10-(J15+J14))/J10</f>
         <v>0.73</v>
       </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10">
-        <f t="shared" ref="O37:R37" si="48">(O10-(O15+O14))/O10</f>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10">
+        <f t="shared" ref="Q37:T37" si="49">(Q10-(Q15+Q14))/Q10</f>
         <v>0.66422575459903554</v>
       </c>
-      <c r="P37" s="10">
-        <f t="shared" si="48"/>
+      <c r="R37" s="10">
+        <f t="shared" si="49"/>
         <v>0.61470275381160622</v>
       </c>
-      <c r="Q37" s="10">
-        <f t="shared" si="48"/>
+      <c r="S37" s="10">
+        <f t="shared" si="49"/>
         <v>0.69591254752851717</v>
       </c>
-      <c r="R37" s="10">
-        <f t="shared" si="48"/>
-        <v>0.73199199569405315</v>
-      </c>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
+      <c r="T37" s="10">
+        <f t="shared" si="49"/>
+        <v>0.72175922105784307</v>
+      </c>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
@@ -3725,15 +3829,17 @@
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
       <c r="AB37" s="10"/>
-      <c r="AD37" t="s">
+      <c r="AC37" s="10"/>
+      <c r="AD37" s="10"/>
+      <c r="AF37" t="s">
         <v>46</v>
       </c>
-      <c r="AE37" s="2">
-        <f>NPV(AE36,R25:EQ25)</f>
-        <v>7078.1785241903008</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="AG37" s="2">
+        <f>NPV(AG36,T25:ES25)</f>
+        <v>6387.2824952179935</v>
+      </c>
+    </row>
+    <row r="38" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>39</v>
       </c>
@@ -3741,45 +3847,45 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10">
-        <f t="shared" ref="F38:I38" si="49">(F11-F13)/F11</f>
+        <f t="shared" ref="F38:I38" si="50">(F11-F13)/F11</f>
         <v>0.84380305602716477</v>
       </c>
       <c r="G38" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.74751302700142119</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.73878146661802258</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.7179913535084802</v>
       </c>
       <c r="J38" s="10">
         <f>(J11-J13)/J11</f>
         <v>0.74</v>
       </c>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10">
-        <f t="shared" ref="O38:R38" si="50">(O11-O13)/O11</f>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10">
+        <f t="shared" ref="Q38:T38" si="51">(Q11-Q13)/Q11</f>
         <v>1</v>
       </c>
-      <c r="P38" s="10">
-        <f t="shared" si="50"/>
+      <c r="R38" s="10">
+        <f t="shared" si="51"/>
         <v>0.86520146520146513</v>
       </c>
-      <c r="Q38" s="10">
-        <f t="shared" si="50"/>
+      <c r="S38" s="10">
+        <f t="shared" si="51"/>
         <v>0.7425803792250617</v>
       </c>
-      <c r="R38" s="10">
-        <f t="shared" si="50"/>
-        <v>0.72984265165421425</v>
-      </c>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
+      <c r="T38" s="10">
+        <f t="shared" si="51"/>
+        <v>0.72875652027595494</v>
+      </c>
       <c r="U38" s="10"/>
       <c r="V38" s="10"/>
       <c r="W38" s="10"/>
@@ -3788,127 +3894,131 @@
       <c r="Z38" s="10"/>
       <c r="AA38" s="10"/>
       <c r="AB38" s="10"/>
-      <c r="AD38" t="s">
+      <c r="AC38" s="10"/>
+      <c r="AD38" s="10"/>
+      <c r="AF38" t="s">
         <v>47</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <f>Main!D8</f>
-        <v>4869.2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.3">
+        <v>5985.7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" ref="C39:J39" si="51">C17/C12</f>
+        <f t="shared" ref="C39:J39" si="52">C17/C12</f>
         <v>0.6765974127793023</v>
       </c>
       <c r="D39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.65066225165562908</v>
       </c>
       <c r="E39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.63061763999038689</v>
       </c>
       <c r="F39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.66337157987643425</v>
       </c>
       <c r="G39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.68927111236430283</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.72895277207392195</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.7286578534617969</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.73361588628624663</v>
       </c>
-      <c r="L39" s="10">
-        <f>L17/L12</f>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="N39" s="10">
+        <f>N17/N12</f>
         <v>0.62057335581787521</v>
       </c>
-      <c r="M39" s="10">
-        <f>M17/M12</f>
+      <c r="O39" s="10">
+        <f>O17/O12</f>
         <v>0.62161269001982822</v>
       </c>
-      <c r="N39" s="10">
-        <f t="shared" ref="N39:AB39" si="52">N17/N12</f>
+      <c r="P39" s="10">
+        <f t="shared" ref="P39:AD39" si="53">P17/P12</f>
         <v>0.61876484560570066</v>
       </c>
-      <c r="O39" s="10">
-        <f t="shared" si="52"/>
+      <c r="Q39" s="10">
+        <f t="shared" si="53"/>
         <v>0.66253814395979183</v>
       </c>
-      <c r="P39" s="10">
-        <f t="shared" si="52"/>
+      <c r="R39" s="10">
+        <f t="shared" si="53"/>
         <v>0.64950132302055774</v>
       </c>
-      <c r="Q39" s="10">
-        <f t="shared" si="52"/>
+      <c r="S39" s="10">
+        <f t="shared" si="53"/>
         <v>0.71064272703616971</v>
       </c>
-      <c r="R39" s="10">
-        <f t="shared" si="52"/>
-        <v>0.73124026247305263</v>
-      </c>
-      <c r="S39" s="10">
-        <f t="shared" si="52"/>
+      <c r="T39" s="10">
+        <f t="shared" si="53"/>
+        <v>0.72406156571808211</v>
+      </c>
+      <c r="U39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="T39" s="10">
-        <f t="shared" si="52"/>
+      <c r="V39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="U39" s="10">
-        <f t="shared" si="52"/>
+      <c r="W39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="V39" s="10">
-        <f t="shared" si="52"/>
+      <c r="X39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="W39" s="10">
-        <f t="shared" si="52"/>
+      <c r="Y39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="X39" s="10">
-        <f t="shared" si="52"/>
+      <c r="Z39" s="10">
+        <f t="shared" si="53"/>
         <v>0.74</v>
       </c>
-      <c r="Y39" s="10">
-        <f t="shared" si="52"/>
+      <c r="AA39" s="10">
+        <f t="shared" si="53"/>
+        <v>0.74</v>
+      </c>
+      <c r="AB39" s="10">
+        <f t="shared" si="53"/>
         <v>0.73999999999999988</v>
       </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="52"/>
-        <v>0.74</v>
-      </c>
-      <c r="AA39" s="10">
-        <f t="shared" si="52"/>
-        <v>0.74</v>
-      </c>
-      <c r="AB39" s="10">
-        <f t="shared" si="52"/>
-        <v>0.7400000000000001</v>
-      </c>
-      <c r="AD39" t="s">
+      <c r="AC39" s="10">
+        <f t="shared" si="53"/>
+        <v>0.73999999999999988</v>
+      </c>
+      <c r="AD39" s="10">
+        <f t="shared" si="53"/>
+        <v>0.73999999999999988</v>
+      </c>
+      <c r="AF39" t="s">
         <v>48</v>
       </c>
-      <c r="AE39" s="2">
-        <f>AE37+AE38</f>
-        <v>11947.378524190301</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="AG39" s="2">
+        <f>AG37+AG38</f>
+        <v>12372.982495217993</v>
+      </c>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>41</v>
       </c>
@@ -3919,431 +4029,439 @@
         <v>0.41195795006570313</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" ref="F40:J40" si="53">F18/D18-1</f>
+        <f t="shared" ref="F40:J40" si="54">F18/D18-1</f>
         <v>0.65248226950354637</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.37971149371800839</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.14234620886981375</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.2367622259696458</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.18999999999999995</v>
       </c>
+      <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="10">
-        <f>M18/L18-1</f>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10">
+        <f>O18/N18-1</f>
         <v>0.6964824120603017</v>
       </c>
-      <c r="N40" s="10">
-        <f t="shared" ref="N40:AB40" si="54">N18/M18-1</f>
+      <c r="P40" s="10">
+        <f t="shared" ref="P40:AD40" si="55">P18/O18-1</f>
         <v>0.2885071090047393</v>
       </c>
-      <c r="O40" s="10">
-        <f t="shared" si="54"/>
+      <c r="Q40" s="10">
+        <f t="shared" si="55"/>
         <v>0.47770114942528719</v>
       </c>
-      <c r="P40" s="10">
-        <f t="shared" si="54"/>
+      <c r="R40" s="10">
+        <f t="shared" si="55"/>
         <v>0.53858120721841951</v>
       </c>
-      <c r="Q40" s="10">
-        <f t="shared" si="54"/>
+      <c r="S40" s="10">
+        <f t="shared" si="55"/>
         <v>0.24550050556117275</v>
       </c>
-      <c r="R40" s="10">
-        <f t="shared" si="54"/>
-        <v>0.21251177139145971</v>
-      </c>
-      <c r="S40" s="10">
-        <f t="shared" si="54"/>
+      <c r="T40" s="10">
+        <f t="shared" si="55"/>
+        <v>0.24792985874330253</v>
+      </c>
+      <c r="U40" s="10">
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="T40" s="10">
-        <f t="shared" si="54"/>
+      <c r="V40" s="10">
+        <f t="shared" si="55"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="U40" s="10">
-        <f t="shared" si="54"/>
+      <c r="W40" s="10">
+        <f t="shared" si="55"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="V40" s="10">
-        <f t="shared" si="54"/>
+      <c r="X40" s="10">
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="W40" s="10">
-        <f t="shared" si="54"/>
+      <c r="Y40" s="10">
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="X40" s="10">
-        <f t="shared" si="54"/>
+      <c r="Z40" s="10">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Y40" s="10">
-        <f t="shared" si="54"/>
+      <c r="AA40" s="10">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="Z40" s="10">
-        <f t="shared" si="54"/>
+      <c r="AB40" s="10">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AA40" s="10">
-        <f t="shared" si="54"/>
+      <c r="AC40" s="10">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB40" s="10">
-        <f t="shared" si="54"/>
+      <c r="AD40" s="10">
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD40" t="s">
+      <c r="AF40" t="s">
         <v>49</v>
       </c>
-      <c r="AE40" s="1">
-        <f>AE39/AB26</f>
-        <v>11.609540884452727</v>
-      </c>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="AG40" s="1">
+        <f>AG39/AD26</f>
+        <v>11.987001061052114</v>
+      </c>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41:J41" si="55">C21/C12</f>
+        <f t="shared" ref="C41:J41" si="56">C21/C12</f>
         <v>8.3496667973343902E-2</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>9.0728476821191922E-2</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13217976447969232</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.18040600176522503</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.28704356407725928</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.36030921608889965</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.3382254089177682</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.36353706497810984</v>
       </c>
-      <c r="L41" s="10">
-        <f>L21/L12</f>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="N41" s="10">
+        <f>N21/N12</f>
         <v>6.8577852726250735E-2</v>
       </c>
-      <c r="M41" s="10">
-        <f>M21/M12</f>
+      <c r="O41" s="10">
+        <f>O21/O12</f>
         <v>7.666886979510909E-2</v>
       </c>
-      <c r="N41" s="10">
-        <f t="shared" ref="N41:AB41" si="56">N21/N12</f>
+      <c r="P41" s="10">
+        <f t="shared" ref="P41:AD41" si="57">P21/P12</f>
         <v>0.10665083135391924</v>
       </c>
-      <c r="O41" s="10">
-        <f t="shared" si="56"/>
+      <c r="Q41" s="10">
+        <f t="shared" si="57"/>
         <v>8.7416980793394439E-2</v>
       </c>
-      <c r="P41" s="10">
-        <f t="shared" si="56"/>
+      <c r="R41" s="10">
+        <f t="shared" si="57"/>
         <v>0.15998371667005906</v>
       </c>
-      <c r="Q41" s="10">
-        <f t="shared" si="56"/>
+      <c r="S41" s="10">
+        <f t="shared" si="57"/>
         <v>0.32650273224043719</v>
       </c>
-      <c r="R41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.35140907490273204</v>
-      </c>
-      <c r="S41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34878878074043618</v>
-      </c>
       <c r="T41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34160788026804007</v>
+        <f t="shared" si="57"/>
+        <v>0.32089469604694931</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.33716147176213229</v>
+        <f t="shared" si="57"/>
+        <v>0.3236915717720687</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.33811675419525972</v>
+        <f t="shared" si="57"/>
+        <v>0.31603797334418154</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.33925708115680325</v>
+        <f t="shared" si="57"/>
+        <v>0.31134255384285875</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34194134732462617</v>
+        <f t="shared" si="57"/>
+        <v>0.31253796886835594</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34208566999014756</v>
+        <f t="shared" si="57"/>
+        <v>0.31392266932810253</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34223140758376247</v>
+        <f t="shared" si="57"/>
+        <v>0.31685477456460359</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34237857397731453</v>
+        <f t="shared" si="57"/>
+        <v>0.31700095384686583</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.34252718317864672</v>
-      </c>
-      <c r="AD41" t="s">
+        <f t="shared" si="57"/>
+        <v>0.31714856625934623</v>
+      </c>
+      <c r="AC41" s="10">
+        <f t="shared" si="57"/>
+        <v>0.31729762585234123</v>
+      </c>
+      <c r="AD41" s="10">
+        <f t="shared" si="57"/>
+        <v>0.31744814681389499</v>
+      </c>
+      <c r="AF41" t="s">
         <v>50</v>
       </c>
-      <c r="AE41" s="1">
+      <c r="AG41" s="1">
         <f>Main!D3</f>
-        <v>11.17</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.3">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>32</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" ref="C42:J42" si="57">C24/C23</f>
+        <f t="shared" ref="C42:J42" si="58">C24/C23</f>
         <v>0.32446808510638242</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.19521912350597645</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.27290448343079937</v>
       </c>
       <c r="F42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.19432773109243701</v>
       </c>
       <c r="G42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.27637673700463206</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.25461511668408215</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.25709401709401719</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="57"/>
-        <v>0.25</v>
-      </c>
-      <c r="L42" s="10">
-        <f>L24/L23</f>
-        <v>-1.9801980198019788E-2</v>
-      </c>
-      <c r="M42" s="10">
-        <f>M24/M23</f>
-        <v>0.26999999999999985</v>
-      </c>
-      <c r="N42" s="10">
-        <f t="shared" ref="N42:AB42" si="58">N24/N23</f>
-        <v>0.2481751824817518</v>
-      </c>
-      <c r="O42" s="10">
-        <f t="shared" si="58"/>
-        <v>0.25056947608200431</v>
-      </c>
-      <c r="P42" s="10">
-        <f t="shared" si="58"/>
-        <v>0.2218430034129692</v>
-      </c>
-      <c r="Q42" s="10">
-        <f t="shared" si="58"/>
-        <v>0.26339842127129198</v>
-      </c>
-      <c r="R42" s="10">
-        <f t="shared" si="58"/>
-        <v>0.25327556468525164</v>
-      </c>
-      <c r="S42" s="10">
         <f t="shared" si="58"/>
         <v>0.25</v>
       </c>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="N42" s="10">
+        <f>N24/N23</f>
+        <v>-1.9801980198019788E-2</v>
+      </c>
+      <c r="O42" s="10">
+        <f>O24/O23</f>
+        <v>0.26999999999999985</v>
+      </c>
+      <c r="P42" s="10">
+        <f t="shared" ref="P42:AD42" si="59">P24/P23</f>
+        <v>0.2481751824817518</v>
+      </c>
+      <c r="Q42" s="10">
+        <f t="shared" si="59"/>
+        <v>0.25056947608200431</v>
+      </c>
+      <c r="R42" s="10">
+        <f t="shared" si="59"/>
+        <v>0.2218430034129692</v>
+      </c>
+      <c r="S42" s="10">
+        <f t="shared" si="59"/>
+        <v>0.26339842127129198</v>
+      </c>
       <c r="T42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
+        <v>0.26221671388101986</v>
+      </c>
+      <c r="U42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="U42" s="10">
-        <f t="shared" si="58"/>
+      <c r="V42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="V42" s="10">
-        <f t="shared" si="58"/>
+      <c r="W42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="W42" s="10">
-        <f t="shared" si="58"/>
+      <c r="X42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="X42" s="10">
-        <f t="shared" si="58"/>
+      <c r="Y42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="Y42" s="10">
-        <f t="shared" si="58"/>
+      <c r="Z42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="Z42" s="10">
-        <f t="shared" si="58"/>
+      <c r="AA42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AA42" s="10">
-        <f t="shared" si="58"/>
+      <c r="AB42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AB42" s="10">
-        <f t="shared" si="58"/>
+      <c r="AC42" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AD42" s="8" t="s">
+      <c r="AD42" s="10">
+        <f t="shared" si="59"/>
+        <v>0.25</v>
+      </c>
+      <c r="AF42" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="AE42" s="11">
-        <f>AE40/AE41-1</f>
-        <v>3.9350123943842963E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.3">
+      <c r="AG42" s="11">
+        <f>AG40/AG41-1</f>
+        <v>0.16378651078175865</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="10">
-        <f t="shared" ref="C43:J43" si="59">C25/C12</f>
+        <f t="shared" ref="C43:J43" si="60">C25/C12</f>
         <v>4.9784398275186326E-2</v>
       </c>
       <c r="D43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.6887417218542911E-2</v>
       </c>
       <c r="E43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.9641913001682214E-2</v>
       </c>
       <c r="F43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.13539276257722857</v>
       </c>
       <c r="G43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.19822360073311712</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.25848532431453081</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.24344611248039427</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.26356278908704156</v>
       </c>
-      <c r="L43" s="10">
-        <f>L25/L12</f>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="N43" s="10">
+        <f>N25/N12</f>
         <v>5.7897695334457593E-2</v>
       </c>
-      <c r="M43" s="10">
-        <f>M25/M12</f>
+      <c r="O43" s="10">
+        <f>O25/O12</f>
         <v>4.8248512888301433E-2</v>
       </c>
-      <c r="N43" s="10">
-        <f t="shared" ref="N43:AB43" si="60">N25/N12</f>
+      <c r="P43" s="10">
+        <f t="shared" ref="P43:AD43" si="61">P25/P12</f>
         <v>7.3396674584323043E-2</v>
       </c>
-      <c r="O43" s="10">
-        <f t="shared" si="60"/>
+      <c r="Q43" s="10">
+        <f t="shared" si="61"/>
         <v>5.9055824807036521E-2</v>
       </c>
-      <c r="P43" s="10">
-        <f t="shared" si="60"/>
+      <c r="R43" s="10">
+        <f t="shared" si="61"/>
         <v>0.11601872582943218</v>
       </c>
-      <c r="Q43" s="10">
-        <f t="shared" si="60"/>
+      <c r="S43" s="10">
+        <f t="shared" si="61"/>
         <v>0.23067915690866514</v>
       </c>
-      <c r="R43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.25392395496044862</v>
-      </c>
-      <c r="S43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.25382986764096443</v>
-      </c>
       <c r="T43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24896155102904949</v>
+        <f t="shared" si="61"/>
+        <v>0.23070534824493408</v>
       </c>
       <c r="U43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24589756181492634</v>
+        <f t="shared" si="61"/>
+        <v>0.23716638989245739</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.2466999037950246</v>
+        <f t="shared" si="61"/>
+        <v>0.23179862267575424</v>
       </c>
       <c r="W43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24757469246964328</v>
+        <f t="shared" si="61"/>
+        <v>0.22847256673508484</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24956453935523457</v>
+        <f t="shared" si="61"/>
+        <v>0.22943312357519649</v>
       </c>
       <c r="Y43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.2496052179118439</v>
+        <f t="shared" si="61"/>
+        <v>0.23048774964869878</v>
       </c>
       <c r="Z43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24964629527783189</v>
+        <f t="shared" si="61"/>
+        <v>0.23267098532653704</v>
       </c>
       <c r="AA43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24968777536309411</v>
+        <f t="shared" si="61"/>
+        <v>0.23273189336081299</v>
       </c>
       <c r="AB43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.24972966211585901</v>
-      </c>
-      <c r="AD43" t="s">
+        <f t="shared" si="61"/>
+        <v>0.2327933985326798</v>
+      </c>
+      <c r="AC43" s="10">
+        <f t="shared" si="61"/>
+        <v>0.23285550669642774</v>
+      </c>
+      <c r="AD43" s="10">
+        <f t="shared" si="61"/>
+        <v>0.23291822376374177</v>
+      </c>
+      <c r="AF43" t="s">
         <v>52</v>
       </c>
-      <c r="AE43" s="4" t="s">
-        <v>63</v>
+      <c r="AG43" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/WISE.xlsx
+++ b/Financial Analysis/WISE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4901FB-EDCA-4971-844B-9446C54A7208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F1D7B-CE08-4482-AED9-50ECDB565E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DF2D7ED4-E95E-4EA0-AAC3-7C5D2EE7EFC0}"/>
   </bookViews>
@@ -757,14 +757,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
       <c r="F3" s="6">
-        <v>45824</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45825</v>
+        <v>45937</v>
       </c>
       <c r="H3" s="6">
         <v>45967</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>10631.660000000002</v>
+        <v>10404.576000000001</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.3">
@@ -830,7 +830,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>4645.9600000000019</v>
+        <v>4418.8760000000011</v>
       </c>
     </row>
   </sheetData>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AG41" s="1">
         <f>Main!D3</f>
-        <v>10.3</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.3">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="AG42" s="11">
         <f>AG40/AG41-1</f>
-        <v>0.16378651078175865</v>
+        <v>0.1891866131996145</v>
       </c>
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.3">

--- a/Financial Analysis/WISE.xlsx
+++ b/Financial Analysis/WISE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F1D7B-CE08-4482-AED9-50ECDB565E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF9483D-EDC3-4BB1-8045-2E04AD1C494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DF2D7ED4-E95E-4EA0-AAC3-7C5D2EE7EFC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DF2D7ED4-E95E-4EA0-AAC3-7C5D2EE7EFC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>Price</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Slightly undervalued</t>
+  </si>
+  <si>
+    <t>WISE</t>
   </si>
 </sst>
 </file>
@@ -233,7 +236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,15 +253,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -309,12 +303,11 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -336,14 +329,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -360,8 +353,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7086600" y="7620"/>
-          <a:ext cx="0" cy="6316980"/>
+          <a:off x="9159240" y="7620"/>
+          <a:ext cx="0" cy="8511540"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -734,14 +727,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFFF112-591F-4737-A293-B0DA2A006C30}">
-  <dimension ref="C2:H9"/>
+  <dimension ref="B2:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="8.88671875" customWidth="1"/>
     <col min="6" max="8" width="14.21875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
@@ -752,85 +745,87 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>10.08</v>
+        <v>8.3949999999999996</v>
       </c>
       <c r="F3" s="6">
-        <v>45937</v>
+        <v>45712</v>
       </c>
       <c r="G3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>46077</v>
       </c>
       <c r="H3" s="6">
-        <v>45967</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <f>1032.2</f>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>10404.576000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+        <v>8621.6649999999991</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <f>4654.9+1430.2</f>
-        <v>6085.0999999999995</v>
+        <f>4846.7+1583.2</f>
+        <v>6429.9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <f>1.3+98.1</f>
-        <v>99.399999999999991</v>
+        <f>4.9+198.5</f>
+        <v>203.4</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>5985.7</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+        <v>6226.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>4418.8760000000011</v>
+        <v>2395.1649999999991</v>
       </c>
     </row>
   </sheetData>
@@ -1062,9 +1057,8 @@
       <c r="I4" s="12">
         <v>207.9</v>
       </c>
-      <c r="J4" s="13">
-        <f>H4*1.03</f>
-        <v>210.738</v>
+      <c r="J4" s="15">
+        <v>208.4</v>
       </c>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
@@ -1094,7 +1088,7 @@
       </c>
       <c r="J5" s="12">
         <f t="shared" si="0"/>
-        <v>423.63800000000003</v>
+        <v>421.3</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
@@ -1104,7 +1098,7 @@
       </c>
       <c r="T5" s="2">
         <f>I5+J5</f>
-        <v>842.73800000000006</v>
+        <v>840.40000000000009</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.3">
@@ -1151,9 +1145,8 @@
       <c r="I7" s="12">
         <v>92.8</v>
       </c>
-      <c r="J7" s="13">
-        <f>H7*1.35</f>
-        <v>98.01</v>
+      <c r="J7" s="15">
+        <v>100.9</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
@@ -1183,7 +1176,7 @@
       </c>
       <c r="J8" s="12">
         <f t="shared" si="1"/>
-        <v>195.81</v>
+        <v>198.7</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
@@ -1193,7 +1186,7 @@
       </c>
       <c r="T8" s="2">
         <f>I8+J8</f>
-        <v>368.61</v>
+        <v>371.5</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
@@ -1238,11 +1231,13 @@
       <c r="I10" s="2">
         <v>591.9</v>
       </c>
-      <c r="J10" s="14">
-        <f>J5+J8</f>
-        <v>619.44800000000009</v>
-      </c>
-      <c r="K10" s="2"/>
+      <c r="J10" s="13">
+        <f>T10-I10</f>
+        <v>620.00000000000011</v>
+      </c>
+      <c r="K10" s="13">
+        <v>658</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2">
@@ -1258,44 +1253,44 @@
         <v>1211.9000000000001</v>
       </c>
       <c r="U10" s="2">
-        <f>T10*1.12</f>
-        <v>1357.3280000000002</v>
+        <f>T10*1.11</f>
+        <v>1345.2090000000003</v>
       </c>
       <c r="V10" s="2">
-        <f>U10*1.1</f>
-        <v>1493.0608000000004</v>
+        <f>U10*1.09</f>
+        <v>1466.2778100000005</v>
       </c>
       <c r="W10" s="2">
         <f>V10*1.07</f>
-        <v>1597.5750560000006</v>
+        <v>1568.9172567000007</v>
       </c>
       <c r="X10" s="2">
         <f>W10*1.05</f>
-        <v>1677.4538088000006</v>
+        <v>1647.3631195350008</v>
       </c>
       <c r="Y10" s="2">
         <f>X10*1.04</f>
-        <v>1744.5519611520008</v>
+        <v>1713.257644316401</v>
       </c>
       <c r="Z10" s="2">
         <f>Y10*1.03</f>
-        <v>1796.8885199865608</v>
+        <v>1764.655373645893</v>
       </c>
       <c r="AA10" s="2">
         <f>Z10*1.02</f>
-        <v>1832.8262903862922</v>
+        <v>1799.9484811188108</v>
       </c>
       <c r="AB10" s="2">
         <f t="shared" ref="AB10:AD10" si="2">AA10*1.02</f>
-        <v>1869.4828161940181</v>
+        <v>1835.9474507411871</v>
       </c>
       <c r="AC10" s="2">
         <f t="shared" si="2"/>
-        <v>1906.8724725178986</v>
+        <v>1872.6663997560108</v>
       </c>
       <c r="AD10" s="2">
         <f t="shared" si="2"/>
-        <v>1945.0099219682565</v>
+        <v>1910.119727751131</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
@@ -1328,11 +1323,13 @@
       <c r="I11" s="2">
         <v>300.7</v>
       </c>
-      <c r="J11" s="14">
-        <f>H11*1.28</f>
-        <v>350.84800000000001</v>
-      </c>
-      <c r="K11" s="2"/>
+      <c r="J11" s="13">
+        <f>T11-I11</f>
+        <v>293.59999999999997</v>
+      </c>
+      <c r="K11" s="13">
+        <v>297.39999999999998</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2">
@@ -1350,44 +1347,44 @@
         <v>594.29999999999995</v>
       </c>
       <c r="U11" s="2">
-        <f>T11*1.15</f>
-        <v>683.44499999999994</v>
+        <f>T11*1.01</f>
+        <v>600.24299999999994</v>
       </c>
       <c r="V11" s="2">
-        <f>U11*1.11</f>
-        <v>758.62395000000004</v>
+        <f>U11*1.04</f>
+        <v>624.25271999999995</v>
       </c>
       <c r="W11" s="2">
-        <f>V11*1.07</f>
-        <v>811.72762650000004</v>
+        <f>V11*1.03</f>
+        <v>642.98030159999996</v>
       </c>
       <c r="X11" s="2">
         <f>W11*1.03</f>
-        <v>836.07945529500012</v>
+        <v>662.269710648</v>
       </c>
       <c r="Y11" s="2">
-        <f>X11*1.02</f>
-        <v>852.80104440090008</v>
+        <f t="shared" ref="Y11:AD11" si="3">X11*1.03</f>
+        <v>682.13780196744005</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" ref="Z11:AD11" si="3">Y11*1.02</f>
-        <v>869.85706528891808</v>
+        <f t="shared" si="3"/>
+        <v>702.60193602646325</v>
       </c>
       <c r="AA11" s="2">
         <f t="shared" si="3"/>
-        <v>887.25420659469648</v>
+        <v>723.67999410725713</v>
       </c>
       <c r="AB11" s="2">
         <f t="shared" si="3"/>
-        <v>904.9992907265904</v>
+        <v>745.39039393047483</v>
       </c>
       <c r="AC11" s="2">
         <f t="shared" si="3"/>
-        <v>923.09927654112221</v>
+        <v>767.75210574838911</v>
       </c>
       <c r="AD11" s="2">
         <f t="shared" si="3"/>
-        <v>941.56126207194472</v>
+        <v>790.78466892084077</v>
       </c>
     </row>
     <row r="12" spans="1:30" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -1423,11 +1420,14 @@
         <f t="shared" ref="I12:J12" si="5">I10+I11</f>
         <v>892.59999999999991</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="9">
         <f t="shared" si="5"/>
-        <v>970.29600000000005</v>
-      </c>
-      <c r="K12" s="9"/>
+        <v>913.60000000000014</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" ref="K12" si="6">K10+K11</f>
+        <v>955.4</v>
+      </c>
       <c r="L12" s="9"/>
       <c r="N12" s="9">
         <v>177.9</v>
@@ -1456,43 +1456,43 @@
       </c>
       <c r="U12" s="9">
         <f>U10+U11</f>
-        <v>2040.7730000000001</v>
+        <v>1945.4520000000002</v>
       </c>
       <c r="V12" s="9">
-        <f t="shared" ref="V12:AD12" si="6">V10+V11</f>
-        <v>2251.6847500000003</v>
+        <f t="shared" ref="V12:AD12" si="7">V10+V11</f>
+        <v>2090.5305300000005</v>
       </c>
       <c r="W12" s="9">
-        <f t="shared" si="6"/>
-        <v>2409.3026825000006</v>
+        <f t="shared" si="7"/>
+        <v>2211.8975583000006</v>
       </c>
       <c r="X12" s="9">
-        <f t="shared" si="6"/>
-        <v>2513.533264095001</v>
+        <f t="shared" si="7"/>
+        <v>2309.6328301830008</v>
       </c>
       <c r="Y12" s="9">
-        <f t="shared" si="6"/>
-        <v>2597.3530055529009</v>
+        <f t="shared" si="7"/>
+        <v>2395.395446283841</v>
       </c>
       <c r="Z12" s="9">
-        <f t="shared" si="6"/>
-        <v>2666.7455852754788</v>
+        <f t="shared" si="7"/>
+        <v>2467.2573096723563</v>
       </c>
       <c r="AA12" s="9">
-        <f t="shared" si="6"/>
-        <v>2720.0804969809888</v>
+        <f t="shared" si="7"/>
+        <v>2523.6284752260681</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" si="6"/>
-        <v>2774.4821069206087</v>
+        <f t="shared" si="7"/>
+        <v>2581.337844671662</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" si="6"/>
-        <v>2829.971749059021</v>
+        <f t="shared" si="7"/>
+        <v>2640.4185055043999</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" si="6"/>
-        <v>2886.5711840402014</v>
+        <f t="shared" si="7"/>
+        <v>2700.9043966719719</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
@@ -1523,11 +1523,13 @@
       <c r="I13" s="2">
         <v>84.8</v>
       </c>
-      <c r="J13" s="14">
-        <f>J11*0.26</f>
-        <v>91.220480000000009</v>
-      </c>
-      <c r="K13" s="2"/>
+      <c r="J13" s="13">
+        <f t="shared" ref="J13:K15" si="8">T13-I13</f>
+        <v>76.399999999999991</v>
+      </c>
+      <c r="K13" s="13">
+        <v>73.3</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1583,11 +1585,13 @@
       <c r="I14" s="2">
         <v>152.9</v>
       </c>
-      <c r="J14" s="14">
-        <f>J10*0.26</f>
-        <v>161.05648000000002</v>
-      </c>
-      <c r="K14" s="2"/>
+      <c r="J14" s="13">
+        <f t="shared" si="8"/>
+        <v>175.20000000000002</v>
+      </c>
+      <c r="K14" s="13">
+        <v>173.7</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="N14" s="2">
         <v>66.5</v>
@@ -1649,11 +1653,13 @@
       <c r="I15" s="2">
         <v>4.5</v>
       </c>
-      <c r="J15" s="14">
-        <f>J10*0.01</f>
-        <v>6.1944800000000013</v>
-      </c>
-      <c r="K15" s="2"/>
+      <c r="J15" s="13">
+        <f t="shared" si="8"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K15" s="13">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="N15" s="2">
         <v>1</v>
@@ -1692,106 +1698,109 @@
         <v>24</v>
       </c>
       <c r="C16" s="2">
-        <f t="shared" ref="C16:H16" si="7">C13+C14+C15</f>
+        <f t="shared" ref="C16:H16" si="9">C13+C14+C15</f>
         <v>82.5</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>105.50000000000001</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>153.69999999999999</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>190.7</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>220.4</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>224.4</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" ref="I16:J16" si="8">I13+I14+I15</f>
+        <f t="shared" ref="I16:J16" si="10">I13+I14+I15</f>
         <v>242.2</v>
       </c>
-      <c r="J16" s="14">
-        <f t="shared" si="8"/>
-        <v>258.47144000000003</v>
-      </c>
-      <c r="K16" s="2"/>
+      <c r="J16" s="13">
+        <f t="shared" si="10"/>
+        <v>256.20000000000005</v>
+      </c>
+      <c r="K16" s="13">
+        <f t="shared" ref="K16" si="11">K13+K14+K15</f>
+        <v>251.6</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="N16" s="2">
-        <f t="shared" ref="N16:T16" si="9">N13+N14+N15</f>
+        <f t="shared" ref="N16:T16" si="12">N13+N14+N15</f>
         <v>67.5</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>114.5</v>
       </c>
       <c r="P16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>160.5</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>188</v>
       </c>
       <c r="R16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>344.4</v>
       </c>
       <c r="S16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>444.79999999999995</v>
       </c>
       <c r="T16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>498.40000000000003</v>
       </c>
       <c r="U16" s="2">
         <f>U12-U17</f>
-        <v>530.60098000000016</v>
+        <v>525.27204000000006</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" ref="V16:AD16" si="10">V12-V17</f>
-        <v>585.43803500000013</v>
+        <f t="shared" ref="V16:AD16" si="13">V12-V17</f>
+        <v>543.53793780000024</v>
       </c>
       <c r="W16" s="2">
-        <f t="shared" si="10"/>
-        <v>626.41869745000008</v>
+        <f t="shared" si="13"/>
+        <v>575.0933651580001</v>
       </c>
       <c r="X16" s="2">
-        <f t="shared" si="10"/>
-        <v>653.51864866470032</v>
+        <f t="shared" si="13"/>
+        <v>600.5045358475802</v>
       </c>
       <c r="Y16" s="2">
-        <f t="shared" si="10"/>
-        <v>675.31178144375417</v>
+        <f t="shared" si="13"/>
+        <v>622.80281603379876</v>
       </c>
       <c r="Z16" s="2">
-        <f t="shared" si="10"/>
-        <v>693.35385217162457</v>
+        <f t="shared" si="13"/>
+        <v>641.48690051481276</v>
       </c>
       <c r="AA16" s="2">
-        <f t="shared" si="10"/>
-        <v>707.22092921505714</v>
+        <f t="shared" si="13"/>
+        <v>656.14340355877766</v>
       </c>
       <c r="AB16" s="2">
-        <f t="shared" si="10"/>
-        <v>721.36534779935846</v>
+        <f t="shared" si="13"/>
+        <v>671.14783961463218</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" si="10"/>
-        <v>735.79265475534567</v>
+        <f t="shared" si="13"/>
+        <v>686.50881143114407</v>
       </c>
       <c r="AD16" s="2">
-        <f t="shared" si="10"/>
-        <v>750.50850785045259</v>
+        <f t="shared" si="13"/>
+        <v>702.23514313471264</v>
       </c>
     </row>
     <row r="17" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -1800,106 +1809,109 @@
         <v>25</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:H17" si="11">C12-C16</f>
+        <f t="shared" ref="C17:H17" si="14">C12-C16</f>
         <v>172.60000000000002</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>196.49999999999994</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>262.39999999999998</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>375.8</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>488.9</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>603.5</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" ref="I17:J17" si="12">I12-I16</f>
+        <f t="shared" ref="I17:J17" si="15">I12-I16</f>
         <v>650.39999999999986</v>
       </c>
-      <c r="J17" s="15">
-        <f t="shared" si="12"/>
-        <v>711.82456000000002</v>
-      </c>
-      <c r="K17" s="9"/>
+      <c r="J17" s="9">
+        <f t="shared" si="15"/>
+        <v>657.40000000000009</v>
+      </c>
+      <c r="K17" s="9">
+        <f t="shared" ref="K17" si="16">K12-K16</f>
+        <v>703.8</v>
+      </c>
       <c r="L17" s="9"/>
       <c r="N17" s="9">
-        <f t="shared" ref="N17:T17" si="13">N12-N16</f>
+        <f t="shared" ref="N17:T17" si="17">N12-N16</f>
         <v>110.4</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>188.10000000000002</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>260.5</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>369.1</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>638.20000000000005</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1092.4000000000001</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1307.8</v>
       </c>
       <c r="U17" s="9">
-        <f>U12*0.74</f>
-        <v>1510.17202</v>
+        <f>U12*0.73</f>
+        <v>1420.1799600000002</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17:AD17" si="14">V12*0.74</f>
-        <v>1666.2467150000002</v>
+        <f t="shared" ref="V17:AD17" si="18">V12*0.74</f>
+        <v>1546.9925922000002</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" si="14"/>
-        <v>1782.8839850500005</v>
+        <f t="shared" si="18"/>
+        <v>1636.8041931420005</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" si="14"/>
-        <v>1860.0146154303006</v>
+        <f t="shared" si="18"/>
+        <v>1709.1282943354206</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" si="14"/>
-        <v>1922.0412241091467</v>
+        <f t="shared" si="18"/>
+        <v>1772.5926302500422</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" si="14"/>
-        <v>1973.3917331038542</v>
+        <f t="shared" si="18"/>
+        <v>1825.7704091575436</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" si="14"/>
-        <v>2012.8595677659316</v>
+        <f t="shared" si="18"/>
+        <v>1867.4850716672904</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" si="14"/>
-        <v>2053.1167591212502</v>
+        <f t="shared" si="18"/>
+        <v>1910.1900050570298</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" si="14"/>
-        <v>2094.1790943036754</v>
+        <f t="shared" si="18"/>
+        <v>1953.9096940732559</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" si="14"/>
-        <v>2136.0626761897488</v>
+        <f t="shared" si="18"/>
+        <v>1998.6692535372592</v>
       </c>
     </row>
     <row r="18" spans="1:149" x14ac:dyDescent="0.3">
@@ -1930,11 +1942,13 @@
       <c r="I18" s="2">
         <v>366.7</v>
       </c>
-      <c r="J18" s="14">
-        <f>H18*1.19</f>
-        <v>380.08599999999996</v>
-      </c>
-      <c r="K18" s="2"/>
+      <c r="J18" s="13">
+        <f t="shared" ref="J18:K20" si="19">T18-I18</f>
+        <v>401.90000000000003</v>
+      </c>
+      <c r="K18" s="13">
+        <v>465.9</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="N18" s="2">
         <v>99.5</v>
@@ -1958,44 +1972,44 @@
         <v>768.6</v>
       </c>
       <c r="U18" s="2">
-        <f>T18*1.15</f>
-        <v>883.89</v>
+        <f>T18*1.24</f>
+        <v>953.06400000000008</v>
       </c>
       <c r="V18" s="2">
         <f>U18*1.12</f>
-        <v>989.95680000000004</v>
+        <v>1067.4316800000001</v>
       </c>
       <c r="W18" s="2">
-        <f>V18*1.08</f>
-        <v>1069.1533440000001</v>
+        <f>V18*1.07</f>
+        <v>1142.1518976000002</v>
       </c>
       <c r="X18" s="2">
-        <f>W18*1.04</f>
-        <v>1111.9194777600001</v>
+        <f>W18*1.05</f>
+        <v>1199.2594924800003</v>
       </c>
       <c r="Y18" s="2">
         <f>X18*1.03</f>
-        <v>1145.2770620928002</v>
+        <v>1235.2372772544004</v>
       </c>
       <c r="Z18" s="2">
         <f>Y18*1.02</f>
-        <v>1168.1826033346563</v>
+        <v>1259.9420227994883</v>
       </c>
       <c r="AA18" s="2">
-        <f t="shared" ref="AA18:AD18" si="15">Z18*1.02</f>
-        <v>1191.5462554013495</v>
+        <f t="shared" ref="AA18:AD18" si="20">Z18*1.02</f>
+        <v>1285.1408632554781</v>
       </c>
       <c r="AB18" s="2">
-        <f t="shared" si="15"/>
-        <v>1215.3771805093766</v>
+        <f t="shared" si="20"/>
+        <v>1310.8436805205877</v>
       </c>
       <c r="AC18" s="2">
-        <f t="shared" si="15"/>
-        <v>1239.6847241195642</v>
+        <f t="shared" si="20"/>
+        <v>1337.0605541309994</v>
       </c>
       <c r="AD18" s="2">
-        <f t="shared" si="15"/>
-        <v>1264.4784186019556</v>
+        <f t="shared" si="20"/>
+        <v>1363.8017652136195</v>
       </c>
     </row>
     <row r="19" spans="1:149" x14ac:dyDescent="0.3">
@@ -2026,10 +2040,13 @@
       <c r="I19" s="2">
         <v>-15.9</v>
       </c>
-      <c r="J19" s="14">
-        <v>-18</v>
-      </c>
-      <c r="K19" s="2"/>
+      <c r="J19" s="13">
+        <f t="shared" si="19"/>
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="K19" s="13">
+        <v>-23.7</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="N19" s="2">
         <v>-0.9</v>
@@ -2059,39 +2076,39 @@
         <v>-34.298999999999999</v>
       </c>
       <c r="V19" s="2">
-        <f t="shared" ref="V19:AD19" si="16">U19*1.03</f>
+        <f t="shared" ref="V19:AD19" si="21">U19*1.03</f>
         <v>-35.327970000000001</v>
       </c>
       <c r="W19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-36.387809099999998</v>
       </c>
       <c r="X19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-37.479443373000002</v>
       </c>
       <c r="Y19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-38.603826674190003</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-39.761941474415707</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-40.954799718648182</v>
       </c>
       <c r="AB19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-42.183443710207627</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-43.44894702151386</v>
       </c>
       <c r="AD19" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-44.752415432159275</v>
       </c>
     </row>
@@ -2123,10 +2140,13 @@
       <c r="I20" s="2">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="J20" s="14">
-        <v>-3</v>
-      </c>
-      <c r="K20" s="2"/>
+      <c r="J20" s="13">
+        <f t="shared" si="19"/>
+        <v>-4.8</v>
+      </c>
+      <c r="K20" s="13">
+        <v>-3.8</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="N20" s="2">
         <v>-0.4</v>
@@ -2187,106 +2207,109 @@
         <v>29</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:J21" si="17">C17-C18-C19-C20</f>
+        <f t="shared" ref="C21:J21" si="22">C17-C18-C19-C20</f>
         <v>21.300000000000033</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>27.399999999999956</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>54.999999999999972</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>102.19999999999999</v>
       </c>
       <c r="G21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>203.6</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>298.3</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>301.89999999999986</v>
       </c>
-      <c r="J21" s="15">
-        <f t="shared" si="17"/>
-        <v>352.73856000000006</v>
-      </c>
-      <c r="K21" s="9"/>
+      <c r="J21" s="9">
+        <f t="shared" si="22"/>
+        <v>277.70000000000005</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" ref="K21" si="23">K17-K18-K19-K20</f>
+        <v>265.39999999999998</v>
+      </c>
       <c r="L21" s="9"/>
       <c r="N21" s="9">
-        <f t="shared" ref="N21:U21" si="18">N17-N18-N19-N20</f>
+        <f t="shared" ref="N21:U21" si="24">N17-N18-N19-N20</f>
         <v>12.200000000000006</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>23.200000000000014</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>44.9</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>48.700000000000045</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>157.20000000000005</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>501.90000000000009</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>579.59999999999991</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="18"/>
-        <v>660.58101999999997</v>
+        <f t="shared" si="24"/>
+        <v>501.41496000000006</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" ref="V21:AD21" si="19">V17-V18-V19-V20</f>
-        <v>711.61788500000023</v>
+        <f t="shared" ref="V21:AD21" si="25">V17-V18-V19-V20</f>
+        <v>514.88888220000013</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="19"/>
-        <v>750.11845015000051</v>
+        <f t="shared" si="25"/>
+        <v>531.0401046420003</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="19"/>
-        <v>785.57458104330055</v>
+        <f t="shared" si="25"/>
+        <v>547.3482452284203</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="19"/>
-        <v>815.36798869053655</v>
+        <f t="shared" si="25"/>
+        <v>575.95917966983188</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="19"/>
-        <v>844.97107124361366</v>
+        <f t="shared" si="25"/>
+        <v>605.59032783247096</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="19"/>
-        <v>862.26811208323022</v>
+        <f t="shared" si="25"/>
+        <v>623.29900813046049</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="19"/>
-        <v>879.92302232208124</v>
+        <f t="shared" si="25"/>
+        <v>641.52976824664972</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="19"/>
-        <v>897.94331720562502</v>
+        <f t="shared" si="25"/>
+        <v>660.29808696377029</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="19"/>
-        <v>916.33667301995251</v>
+        <f t="shared" si="25"/>
+        <v>679.61990375579899</v>
       </c>
     </row>
     <row r="22" spans="1:149" x14ac:dyDescent="0.3">
@@ -2317,11 +2340,13 @@
       <c r="I22" s="2">
         <v>9.4</v>
       </c>
-      <c r="J22" s="14">
-        <f>H22*1.05</f>
-        <v>11.76</v>
-      </c>
-      <c r="K22" s="2"/>
+      <c r="J22" s="13">
+        <f>T22-I22</f>
+        <v>5.4</v>
+      </c>
+      <c r="K22" s="13">
+        <v>10.8</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="N22" s="2">
         <v>2.1</v>
@@ -2350,39 +2375,39 @@
         <v>15.244000000000002</v>
       </c>
       <c r="V22" s="2">
-        <f t="shared" ref="V22:AD22" si="20">U22*1.03</f>
+        <f t="shared" ref="V22:AD22" si="26">U22*1.03</f>
         <v>15.701320000000003</v>
       </c>
       <c r="W22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>16.172359600000004</v>
       </c>
       <c r="X22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>16.657530388000005</v>
       </c>
       <c r="Y22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>17.157256299640007</v>
       </c>
       <c r="Z22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>17.671973988629208</v>
       </c>
       <c r="AA22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>18.202133208288085</v>
       </c>
       <c r="AB22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>18.74819720453673</v>
       </c>
       <c r="AC22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>19.310643120672832</v>
       </c>
       <c r="AD22" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>19.889962414293016</v>
       </c>
     </row>
@@ -2392,106 +2417,109 @@
         <v>31</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:H23" si="21">C21-C22</f>
+        <f t="shared" ref="C23:H23" si="27">C21-C22</f>
         <v>18.800000000000033</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>25.099999999999955</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>51.299999999999969</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>95.199999999999989</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>194.29999999999998</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>287.10000000000002</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23:J23" si="22">I21-I22</f>
+        <f t="shared" ref="I23:J23" si="28">I21-I22</f>
         <v>292.49999999999989</v>
       </c>
-      <c r="J23" s="15">
-        <f t="shared" si="22"/>
-        <v>340.97856000000007</v>
-      </c>
-      <c r="K23" s="9"/>
+      <c r="J23" s="9">
+        <f t="shared" si="28"/>
+        <v>272.30000000000007</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" ref="K23" si="29">K21-K22</f>
+        <v>254.59999999999997</v>
+      </c>
       <c r="L23" s="9"/>
       <c r="N23" s="9">
-        <f t="shared" ref="N23:U23" si="23">N21-N22</f>
+        <f t="shared" ref="N23:U23" si="30">N21-N22</f>
         <v>10.100000000000007</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>20.000000000000014</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>41.1</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>43.900000000000048</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>146.50000000000006</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>481.40000000000009</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>564.79999999999995</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="23"/>
-        <v>645.33701999999994</v>
+        <f t="shared" si="30"/>
+        <v>486.17096000000004</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23:AD23" si="24">V21-V22</f>
-        <v>695.91656500000022</v>
+        <f t="shared" ref="V23:AD23" si="31">V21-V22</f>
+        <v>499.18756220000012</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="24"/>
-        <v>733.94609055000046</v>
+        <f t="shared" si="31"/>
+        <v>514.86774504200025</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="24"/>
-        <v>768.9170506553005</v>
+        <f t="shared" si="31"/>
+        <v>530.69071484042024</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="24"/>
-        <v>798.21073239089651</v>
+        <f t="shared" si="31"/>
+        <v>558.80192337019184</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="24"/>
-        <v>827.29909725498442</v>
+        <f t="shared" si="31"/>
+        <v>587.91835384384171</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="24"/>
-        <v>844.06597887494218</v>
+        <f t="shared" si="31"/>
+        <v>605.09687492217245</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="24"/>
-        <v>861.17482511754451</v>
+        <f t="shared" si="31"/>
+        <v>622.781571042113</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="24"/>
-        <v>878.63267408495221</v>
+        <f t="shared" si="31"/>
+        <v>640.98744384309748</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="24"/>
-        <v>896.44671060565952</v>
+        <f t="shared" si="31"/>
+        <v>659.72994134150599</v>
       </c>
     </row>
     <row r="24" spans="1:149" x14ac:dyDescent="0.3">
@@ -2522,11 +2550,13 @@
       <c r="I24" s="2">
         <v>75.2</v>
       </c>
-      <c r="J24" s="14">
-        <f>J23*0.25</f>
-        <v>85.244640000000018</v>
-      </c>
-      <c r="K24" s="2"/>
+      <c r="J24" s="13">
+        <f>T24-I24</f>
+        <v>72.899999999999991</v>
+      </c>
+      <c r="K24" s="13">
+        <v>67.400000000000006</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="N24" s="2">
         <v>-0.2</v>
@@ -2551,43 +2581,43 @@
       </c>
       <c r="U24" s="2">
         <f>U23*0.25</f>
-        <v>161.33425499999998</v>
+        <v>121.54274000000001</v>
       </c>
       <c r="V24" s="2">
-        <f t="shared" ref="V24:AD24" si="25">V23*0.25</f>
-        <v>173.97914125000005</v>
+        <f t="shared" ref="V24:AD24" si="32">V23*0.25</f>
+        <v>124.79689055000003</v>
       </c>
       <c r="W24" s="2">
-        <f t="shared" si="25"/>
-        <v>183.48652263750012</v>
+        <f t="shared" si="32"/>
+        <v>128.71693626050006</v>
       </c>
       <c r="X24" s="2">
-        <f t="shared" si="25"/>
-        <v>192.22926266382512</v>
+        <f t="shared" si="32"/>
+        <v>132.67267871010506</v>
       </c>
       <c r="Y24" s="2">
-        <f t="shared" si="25"/>
-        <v>199.55268309772413</v>
+        <f t="shared" si="32"/>
+        <v>139.70048084254796</v>
       </c>
       <c r="Z24" s="2">
-        <f t="shared" si="25"/>
-        <v>206.8247743137461</v>
+        <f t="shared" si="32"/>
+        <v>146.97958846096043</v>
       </c>
       <c r="AA24" s="2">
-        <f t="shared" si="25"/>
-        <v>211.01649471873554</v>
+        <f t="shared" si="32"/>
+        <v>151.27421873054311</v>
       </c>
       <c r="AB24" s="2">
-        <f t="shared" si="25"/>
-        <v>215.29370627938613</v>
+        <f t="shared" si="32"/>
+        <v>155.69539276052825</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="25"/>
-        <v>219.65816852123805</v>
+        <f t="shared" si="32"/>
+        <v>160.24686096077437</v>
       </c>
       <c r="AD24" s="2">
-        <f t="shared" si="25"/>
-        <v>224.11167765141488</v>
+        <f t="shared" si="32"/>
+        <v>164.9324853353765</v>
       </c>
     </row>
     <row r="25" spans="1:149" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -2596,582 +2626,585 @@
         <v>33</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:H25" si="26">C23-C24</f>
+        <f t="shared" ref="C25:H25" si="33">C23-C24</f>
         <v>12.700000000000033</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>20.199999999999953</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>37.299999999999969</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>76.699999999999989</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>140.59999999999997</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>214.00000000000003</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" ref="I25:J25" si="27">I23-I24</f>
+        <f t="shared" ref="I25:J25" si="34">I23-I24</f>
         <v>217.2999999999999</v>
       </c>
-      <c r="J25" s="15">
-        <f t="shared" si="27"/>
-        <v>255.73392000000007</v>
-      </c>
-      <c r="K25" s="9"/>
+      <c r="J25" s="9">
+        <f t="shared" si="34"/>
+        <v>199.40000000000009</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" ref="K25" si="35">K23-K24</f>
+        <v>187.19999999999996</v>
+      </c>
       <c r="L25" s="9"/>
       <c r="N25" s="9">
-        <f t="shared" ref="N25:U25" si="28">N23-N24</f>
+        <f t="shared" ref="N25:U25" si="36">N23-N24</f>
         <v>10.300000000000006</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>14.600000000000014</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>30.900000000000002</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>32.900000000000048</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>114.00000000000006</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>354.60000000000008</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v>416.69999999999993</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="28"/>
-        <v>484.00276499999995</v>
+        <f t="shared" si="36"/>
+        <v>364.62822000000006</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" ref="V25:AD25" si="29">V23-V24</f>
-        <v>521.93742375000011</v>
+        <f t="shared" ref="V25:AD25" si="37">V23-V24</f>
+        <v>374.39067165000006</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="29"/>
-        <v>550.45956791250035</v>
+        <f t="shared" si="37"/>
+        <v>386.15080878150019</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="29"/>
-        <v>576.68778799147537</v>
+        <f t="shared" si="37"/>
+        <v>398.01803613031518</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="29"/>
-        <v>598.65804929317233</v>
+        <f t="shared" si="37"/>
+        <v>419.10144252764388</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="29"/>
-        <v>620.47432294123837</v>
+        <f t="shared" si="37"/>
+        <v>440.93876538288129</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="29"/>
-        <v>633.04948415620663</v>
+        <f t="shared" si="37"/>
+        <v>453.82265619162933</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="29"/>
-        <v>645.88111883815839</v>
+        <f t="shared" si="37"/>
+        <v>467.08617828158475</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="29"/>
-        <v>658.97450556371416</v>
+        <f t="shared" si="37"/>
+        <v>480.74058288232311</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="29"/>
-        <v>672.33503295424464</v>
+        <f t="shared" si="37"/>
+        <v>494.79745600612949</v>
       </c>
       <c r="AE25" s="8">
         <f>AD25+(AD25*$AG$35)</f>
-        <v>665.61168262470221</v>
+        <v>489.84948144606818</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" ref="AF25:CQ25" si="30">AE25+(AE25*$AG$35)</f>
-        <v>658.95556579845515</v>
+        <f t="shared" ref="AF25:CQ25" si="38">AE25+(AE25*$AG$35)</f>
+        <v>484.95098663160752</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" si="30"/>
-        <v>652.36601014047062</v>
+        <f t="shared" si="38"/>
+        <v>480.10147676529147</v>
       </c>
       <c r="AH25" s="8">
-        <f t="shared" si="30"/>
-        <v>645.84235003906588</v>
+        <f t="shared" si="38"/>
+        <v>475.30046199763854</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="30"/>
-        <v>639.38392653867527</v>
+        <f t="shared" si="38"/>
+        <v>470.54745737766217</v>
       </c>
       <c r="AJ25" s="8">
-        <f t="shared" si="30"/>
-        <v>632.99008727328851</v>
+        <f t="shared" si="38"/>
+        <v>465.84198280388557</v>
       </c>
       <c r="AK25" s="8">
-        <f t="shared" si="30"/>
-        <v>626.66018640055563</v>
+        <f t="shared" si="38"/>
+        <v>461.18356297584671</v>
       </c>
       <c r="AL25" s="8">
-        <f t="shared" si="30"/>
-        <v>620.39358453655007</v>
+        <f t="shared" si="38"/>
+        <v>456.57172734608827</v>
       </c>
       <c r="AM25" s="8">
-        <f t="shared" si="30"/>
-        <v>614.18964869118452</v>
+        <f t="shared" si="38"/>
+        <v>452.00601007262736</v>
       </c>
       <c r="AN25" s="8">
-        <f t="shared" si="30"/>
-        <v>608.04775220427268</v>
+        <f t="shared" si="38"/>
+        <v>447.48594997190111</v>
       </c>
       <c r="AO25" s="8">
-        <f t="shared" si="30"/>
-        <v>601.96727468222991</v>
+        <f t="shared" si="38"/>
+        <v>443.0110904721821</v>
       </c>
       <c r="AP25" s="8">
-        <f t="shared" si="30"/>
-        <v>595.94760193540765</v>
+        <f t="shared" si="38"/>
+        <v>438.5809795674603</v>
       </c>
       <c r="AQ25" s="8">
-        <f t="shared" si="30"/>
-        <v>589.9881259160536</v>
+        <f t="shared" si="38"/>
+        <v>434.19516977178569</v>
       </c>
       <c r="AR25" s="8">
-        <f t="shared" si="30"/>
-        <v>584.08824465689304</v>
+        <f t="shared" si="38"/>
+        <v>429.85321807406785</v>
       </c>
       <c r="AS25" s="8">
-        <f t="shared" si="30"/>
-        <v>578.24736221032413</v>
+        <f t="shared" si="38"/>
+        <v>425.55468589332719</v>
       </c>
       <c r="AT25" s="8">
-        <f t="shared" si="30"/>
-        <v>572.4648885882209</v>
+        <f t="shared" si="38"/>
+        <v>421.29913903439393</v>
       </c>
       <c r="AU25" s="8">
-        <f t="shared" si="30"/>
-        <v>566.74023970233873</v>
+        <f t="shared" si="38"/>
+        <v>417.08614764405002</v>
       </c>
       <c r="AV25" s="8">
-        <f t="shared" si="30"/>
-        <v>561.07283730531537</v>
+        <f t="shared" si="38"/>
+        <v>412.91528616760951</v>
       </c>
       <c r="AW25" s="8">
-        <f t="shared" si="30"/>
-        <v>555.46210893226225</v>
+        <f t="shared" si="38"/>
+        <v>408.78613330593339</v>
       </c>
       <c r="AX25" s="8">
-        <f t="shared" si="30"/>
-        <v>549.90748784293964</v>
+        <f t="shared" si="38"/>
+        <v>404.69827197287407</v>
       </c>
       <c r="AY25" s="8">
-        <f t="shared" si="30"/>
-        <v>544.40841296451026</v>
+        <f t="shared" si="38"/>
+        <v>400.65128925314531</v>
       </c>
       <c r="AZ25" s="8">
-        <f t="shared" si="30"/>
-        <v>538.96432883486511</v>
+        <f t="shared" si="38"/>
+        <v>396.64477636061383</v>
       </c>
       <c r="BA25" s="8">
-        <f t="shared" si="30"/>
-        <v>533.57468554651643</v>
+        <f t="shared" si="38"/>
+        <v>392.67832859700769</v>
       </c>
       <c r="BB25" s="8">
-        <f t="shared" si="30"/>
-        <v>528.23893869105132</v>
+        <f t="shared" si="38"/>
+        <v>388.7515453110376</v>
       </c>
       <c r="BC25" s="8">
-        <f t="shared" si="30"/>
-        <v>522.95654930414082</v>
+        <f t="shared" si="38"/>
+        <v>384.86402985792722</v>
       </c>
       <c r="BD25" s="8">
-        <f t="shared" si="30"/>
-        <v>517.72698381109944</v>
+        <f t="shared" si="38"/>
+        <v>381.01538955934797</v>
       </c>
       <c r="BE25" s="8">
-        <f t="shared" si="30"/>
-        <v>512.54971397298846</v>
+        <f t="shared" si="38"/>
+        <v>377.20523566375448</v>
       </c>
       <c r="BF25" s="8">
-        <f t="shared" si="30"/>
-        <v>507.42421683325858</v>
+        <f t="shared" si="38"/>
+        <v>373.43318330711691</v>
       </c>
       <c r="BG25" s="8">
-        <f t="shared" si="30"/>
-        <v>502.34997466492598</v>
+        <f t="shared" si="38"/>
+        <v>369.69885147404574</v>
       </c>
       <c r="BH25" s="8">
-        <f t="shared" si="30"/>
-        <v>497.32647491827674</v>
+        <f t="shared" si="38"/>
+        <v>366.0018629593053</v>
       </c>
       <c r="BI25" s="8">
-        <f t="shared" si="30"/>
-        <v>492.35321016909398</v>
+        <f t="shared" si="38"/>
+        <v>362.34184432971227</v>
       </c>
       <c r="BJ25" s="8">
-        <f t="shared" si="30"/>
-        <v>487.42967806740302</v>
+        <f t="shared" si="38"/>
+        <v>358.71842588641516</v>
       </c>
       <c r="BK25" s="8">
-        <f t="shared" si="30"/>
-        <v>482.55538128672896</v>
+        <f t="shared" si="38"/>
+        <v>355.13124162755099</v>
       </c>
       <c r="BL25" s="8">
-        <f t="shared" si="30"/>
-        <v>477.72982747386169</v>
+        <f t="shared" si="38"/>
+        <v>351.5799292112755</v>
       </c>
       <c r="BM25" s="8">
-        <f t="shared" si="30"/>
-        <v>472.95252919912309</v>
+        <f t="shared" si="38"/>
+        <v>348.06412991916272</v>
       </c>
       <c r="BN25" s="8">
-        <f t="shared" si="30"/>
-        <v>468.22300390713184</v>
+        <f t="shared" si="38"/>
+        <v>344.58348861997109</v>
       </c>
       <c r="BO25" s="8">
-        <f t="shared" si="30"/>
-        <v>463.54077386806051</v>
+        <f t="shared" si="38"/>
+        <v>341.1376537337714</v>
       </c>
       <c r="BP25" s="8">
-        <f t="shared" si="30"/>
-        <v>458.9053661293799</v>
+        <f t="shared" si="38"/>
+        <v>337.72627719643367</v>
       </c>
       <c r="BQ25" s="8">
-        <f t="shared" si="30"/>
-        <v>454.3163124680861</v>
+        <f t="shared" si="38"/>
+        <v>334.34901442446932</v>
       </c>
       <c r="BR25" s="8">
-        <f t="shared" si="30"/>
-        <v>449.77314934340524</v>
+        <f t="shared" si="38"/>
+        <v>331.00552428022462</v>
       </c>
       <c r="BS25" s="8">
-        <f t="shared" si="30"/>
-        <v>445.27541784997118</v>
+        <f t="shared" si="38"/>
+        <v>327.69546903742236</v>
       </c>
       <c r="BT25" s="8">
-        <f t="shared" si="30"/>
-        <v>440.82266367147145</v>
+        <f t="shared" si="38"/>
+        <v>324.41851434704813</v>
       </c>
       <c r="BU25" s="8">
-        <f t="shared" si="30"/>
-        <v>436.41443703475676</v>
+        <f t="shared" si="38"/>
+        <v>321.17432920357766</v>
       </c>
       <c r="BV25" s="8">
-        <f t="shared" si="30"/>
-        <v>432.0502926644092</v>
+        <f t="shared" si="38"/>
+        <v>317.96258591154191</v>
       </c>
       <c r="BW25" s="8">
-        <f t="shared" si="30"/>
-        <v>427.72978973776509</v>
+        <f t="shared" si="38"/>
+        <v>314.78296005242646</v>
       </c>
       <c r="BX25" s="8">
-        <f t="shared" si="30"/>
-        <v>423.45249184038744</v>
+        <f t="shared" si="38"/>
+        <v>311.63513045190217</v>
       </c>
       <c r="BY25" s="8">
-        <f t="shared" si="30"/>
-        <v>419.21796692198359</v>
+        <f t="shared" si="38"/>
+        <v>308.51877914738316</v>
       </c>
       <c r="BZ25" s="8">
-        <f t="shared" si="30"/>
-        <v>415.02578725276373</v>
+        <f t="shared" si="38"/>
+        <v>305.4335913559093</v>
       </c>
       <c r="CA25" s="8">
-        <f t="shared" si="30"/>
-        <v>410.87552938023612</v>
+        <f t="shared" si="38"/>
+        <v>302.3792554423502</v>
       </c>
       <c r="CB25" s="8">
-        <f t="shared" si="30"/>
-        <v>406.76677408643377</v>
+        <f t="shared" si="38"/>
+        <v>299.35546288792671</v>
       </c>
       <c r="CC25" s="8">
-        <f t="shared" si="30"/>
-        <v>402.69910634556942</v>
+        <f t="shared" si="38"/>
+        <v>296.36190825904742</v>
       </c>
       <c r="CD25" s="8">
-        <f t="shared" si="30"/>
-        <v>398.67211528211374</v>
+        <f t="shared" si="38"/>
+        <v>293.39828917645696</v>
       </c>
       <c r="CE25" s="8">
-        <f t="shared" si="30"/>
-        <v>394.6853941292926</v>
+        <f t="shared" si="38"/>
+        <v>290.46430628469238</v>
       </c>
       <c r="CF25" s="8">
-        <f t="shared" si="30"/>
-        <v>390.73854018799966</v>
+        <f t="shared" si="38"/>
+        <v>287.55966322184548</v>
       </c>
       <c r="CG25" s="8">
-        <f t="shared" si="30"/>
-        <v>386.83115478611967</v>
+        <f t="shared" si="38"/>
+        <v>284.68406658962704</v>
       </c>
       <c r="CH25" s="8">
-        <f t="shared" si="30"/>
-        <v>382.96284323825847</v>
+        <f t="shared" si="38"/>
+        <v>281.83722592373078</v>
       </c>
       <c r="CI25" s="8">
-        <f t="shared" si="30"/>
-        <v>379.13321480587587</v>
+        <f t="shared" si="38"/>
+        <v>279.01885366449346</v>
       </c>
       <c r="CJ25" s="8">
-        <f t="shared" si="30"/>
-        <v>375.34188265781711</v>
+        <f t="shared" si="38"/>
+        <v>276.2286651278485</v>
       </c>
       <c r="CK25" s="8">
-        <f t="shared" si="30"/>
-        <v>371.58846383123893</v>
+        <f t="shared" si="38"/>
+        <v>273.46637847657001</v>
       </c>
       <c r="CL25" s="8">
-        <f t="shared" si="30"/>
-        <v>367.87257919292654</v>
+        <f t="shared" si="38"/>
+        <v>270.73171469180431</v>
       </c>
       <c r="CM25" s="8">
-        <f t="shared" si="30"/>
-        <v>364.19385340099728</v>
+        <f t="shared" si="38"/>
+        <v>268.02439754488626</v>
       </c>
       <c r="CN25" s="8">
-        <f t="shared" si="30"/>
-        <v>360.55191486698732</v>
+        <f t="shared" si="38"/>
+        <v>265.34415356943737</v>
       </c>
       <c r="CO25" s="8">
-        <f t="shared" si="30"/>
-        <v>356.94639571831743</v>
+        <f t="shared" si="38"/>
+        <v>262.69071203374301</v>
       </c>
       <c r="CP25" s="8">
-        <f t="shared" si="30"/>
-        <v>353.37693176113424</v>
+        <f t="shared" si="38"/>
+        <v>260.06380491340559</v>
       </c>
       <c r="CQ25" s="8">
-        <f t="shared" si="30"/>
-        <v>349.84316244352289</v>
+        <f t="shared" si="38"/>
+        <v>257.46316686427156</v>
       </c>
       <c r="CR25" s="8">
-        <f t="shared" ref="CR25:ES25" si="31">CQ25+(CQ25*$AG$35)</f>
-        <v>346.34473081908766</v>
+        <f t="shared" ref="CR25:ES25" si="39">CQ25+(CQ25*$AG$35)</f>
+        <v>254.88853519562883</v>
       </c>
       <c r="CS25" s="8">
-        <f t="shared" si="31"/>
-        <v>342.88128351089676</v>
+        <f t="shared" si="39"/>
+        <v>252.33964984367253</v>
       </c>
       <c r="CT25" s="8">
-        <f t="shared" si="31"/>
-        <v>339.45247067578782</v>
+        <f t="shared" si="39"/>
+        <v>249.81625334523579</v>
       </c>
       <c r="CU25" s="8">
-        <f t="shared" si="31"/>
-        <v>336.05794596902996</v>
+        <f t="shared" si="39"/>
+        <v>247.31809081178343</v>
       </c>
       <c r="CV25" s="8">
-        <f t="shared" si="31"/>
-        <v>332.69736650933964</v>
+        <f t="shared" si="39"/>
+        <v>244.84490990366561</v>
       </c>
       <c r="CW25" s="8">
-        <f t="shared" si="31"/>
-        <v>329.37039284424623</v>
+        <f t="shared" si="39"/>
+        <v>242.39646080462896</v>
       </c>
       <c r="CX25" s="8">
-        <f t="shared" si="31"/>
-        <v>326.07668891580374</v>
+        <f t="shared" si="39"/>
+        <v>239.97249619658268</v>
       </c>
       <c r="CY25" s="8">
-        <f t="shared" si="31"/>
-        <v>322.81592202664569</v>
+        <f t="shared" si="39"/>
+        <v>237.57277123461685</v>
       </c>
       <c r="CZ25" s="8">
-        <f t="shared" si="31"/>
-        <v>319.58776280637926</v>
+        <f t="shared" si="39"/>
+        <v>235.19704352227069</v>
       </c>
       <c r="DA25" s="8">
-        <f t="shared" si="31"/>
-        <v>316.39188517831548</v>
+        <f t="shared" si="39"/>
+        <v>232.84507308704798</v>
       </c>
       <c r="DB25" s="8">
-        <f t="shared" si="31"/>
-        <v>313.22796632653234</v>
+        <f t="shared" si="39"/>
+        <v>230.51662235617749</v>
       </c>
       <c r="DC25" s="8">
-        <f t="shared" si="31"/>
-        <v>310.09568666326703</v>
+        <f t="shared" si="39"/>
+        <v>228.21145613261572</v>
       </c>
       <c r="DD25" s="8">
-        <f t="shared" si="31"/>
-        <v>306.99472979663437</v>
+        <f t="shared" si="39"/>
+        <v>225.92934157128957</v>
       </c>
       <c r="DE25" s="8">
-        <f t="shared" si="31"/>
-        <v>303.92478249866804</v>
+        <f t="shared" si="39"/>
+        <v>223.67004815557667</v>
       </c>
       <c r="DF25" s="8">
-        <f t="shared" si="31"/>
-        <v>300.88553467368138</v>
+        <f t="shared" si="39"/>
+        <v>221.43334767402089</v>
       </c>
       <c r="DG25" s="8">
-        <f t="shared" si="31"/>
-        <v>297.87667932694455</v>
+        <f t="shared" si="39"/>
+        <v>219.21901419728067</v>
       </c>
       <c r="DH25" s="8">
-        <f t="shared" si="31"/>
-        <v>294.89791253367508</v>
+        <f t="shared" si="39"/>
+        <v>217.02682405530786</v>
       </c>
       <c r="DI25" s="8">
-        <f t="shared" si="31"/>
-        <v>291.94893340833835</v>
+        <f t="shared" si="39"/>
+        <v>214.85655581475478</v>
       </c>
       <c r="DJ25" s="8">
-        <f t="shared" si="31"/>
-        <v>289.02944407425497</v>
+        <f t="shared" si="39"/>
+        <v>212.70799025660725</v>
       </c>
       <c r="DK25" s="8">
-        <f t="shared" si="31"/>
-        <v>286.13914963351243</v>
+        <f t="shared" si="39"/>
+        <v>210.58091035404118</v>
       </c>
       <c r="DL25" s="8">
-        <f t="shared" si="31"/>
-        <v>283.27775813717733</v>
+        <f t="shared" si="39"/>
+        <v>208.47510125050076</v>
       </c>
       <c r="DM25" s="8">
-        <f t="shared" si="31"/>
-        <v>280.44498055580556</v>
+        <f t="shared" si="39"/>
+        <v>206.39035023799576</v>
       </c>
       <c r="DN25" s="8">
-        <f t="shared" si="31"/>
-        <v>277.64053075024748</v>
+        <f t="shared" si="39"/>
+        <v>204.3264467356158</v>
       </c>
       <c r="DO25" s="8">
-        <f t="shared" si="31"/>
-        <v>274.86412544274498</v>
+        <f t="shared" si="39"/>
+        <v>202.28318226825965</v>
       </c>
       <c r="DP25" s="8">
-        <f t="shared" si="31"/>
-        <v>272.11548418831751</v>
+        <f t="shared" si="39"/>
+        <v>200.26035044557705</v>
       </c>
       <c r="DQ25" s="8">
-        <f t="shared" si="31"/>
-        <v>269.39432934643435</v>
+        <f t="shared" si="39"/>
+        <v>198.25774694112127</v>
       </c>
       <c r="DR25" s="8">
-        <f t="shared" si="31"/>
-        <v>266.70038605296998</v>
+        <f t="shared" si="39"/>
+        <v>196.27516947171006</v>
       </c>
       <c r="DS25" s="8">
-        <f t="shared" si="31"/>
-        <v>264.03338219244029</v>
+        <f t="shared" si="39"/>
+        <v>194.31241777699296</v>
       </c>
       <c r="DT25" s="8">
-        <f t="shared" si="31"/>
-        <v>261.39304837051588</v>
+        <f t="shared" si="39"/>
+        <v>192.36929359922303</v>
       </c>
       <c r="DU25" s="8">
-        <f t="shared" si="31"/>
-        <v>258.77911788681075</v>
+        <f t="shared" si="39"/>
+        <v>190.44560066323081</v>
       </c>
       <c r="DV25" s="8">
-        <f t="shared" si="31"/>
-        <v>256.19132670794266</v>
+        <f t="shared" si="39"/>
+        <v>188.5411446565985</v>
       </c>
       <c r="DW25" s="8">
-        <f t="shared" si="31"/>
-        <v>253.62941344086323</v>
+        <f t="shared" si="39"/>
+        <v>186.65573321003251</v>
       </c>
       <c r="DX25" s="8">
-        <f t="shared" si="31"/>
-        <v>251.09311930645461</v>
+        <f t="shared" si="39"/>
+        <v>184.78917587793219</v>
       </c>
       <c r="DY25" s="8">
-        <f t="shared" si="31"/>
-        <v>248.58218811339006</v>
+        <f t="shared" si="39"/>
+        <v>182.94128411915287</v>
       </c>
       <c r="DZ25" s="8">
-        <f t="shared" si="31"/>
-        <v>246.09636623225617</v>
+        <f t="shared" si="39"/>
+        <v>181.11187127796134</v>
       </c>
       <c r="EA25" s="8">
-        <f t="shared" si="31"/>
-        <v>243.6354025699336</v>
+        <f t="shared" si="39"/>
+        <v>179.30075256518174</v>
       </c>
       <c r="EB25" s="8">
-        <f t="shared" si="31"/>
-        <v>241.19904854423427</v>
+        <f t="shared" si="39"/>
+        <v>177.50774503952991</v>
       </c>
       <c r="EC25" s="8">
-        <f t="shared" si="31"/>
-        <v>238.78705805879193</v>
+        <f t="shared" si="39"/>
+        <v>175.73266758913462</v>
       </c>
       <c r="ED25" s="8">
-        <f t="shared" si="31"/>
-        <v>236.399187478204</v>
+        <f t="shared" si="39"/>
+        <v>173.97534091324329</v>
       </c>
       <c r="EE25" s="8">
-        <f t="shared" si="31"/>
-        <v>234.03519560342195</v>
+        <f t="shared" si="39"/>
+        <v>172.23558750411087</v>
       </c>
       <c r="EF25" s="8">
-        <f t="shared" si="31"/>
-        <v>231.69484364738773</v>
+        <f t="shared" si="39"/>
+        <v>170.51323162906976</v>
       </c>
       <c r="EG25" s="8">
-        <f t="shared" si="31"/>
-        <v>229.37789521091386</v>
+        <f t="shared" si="39"/>
+        <v>168.80809931277906</v>
       </c>
       <c r="EH25" s="8">
-        <f t="shared" si="31"/>
-        <v>227.08411625880473</v>
+        <f t="shared" si="39"/>
+        <v>167.12001831965128</v>
       </c>
       <c r="EI25" s="8">
-        <f t="shared" si="31"/>
-        <v>224.81327509621667</v>
+        <f t="shared" si="39"/>
+        <v>165.44881813645478</v>
       </c>
       <c r="EJ25" s="8">
-        <f t="shared" si="31"/>
-        <v>222.56514234525451</v>
+        <f t="shared" si="39"/>
+        <v>163.79432995509023</v>
       </c>
       <c r="EK25" s="8">
-        <f t="shared" si="31"/>
-        <v>220.33949092180197</v>
+        <f t="shared" si="39"/>
+        <v>162.15638665553934</v>
       </c>
       <c r="EL25" s="8">
-        <f t="shared" si="31"/>
-        <v>218.13609601258395</v>
+        <f t="shared" si="39"/>
+        <v>160.53482278898394</v>
       </c>
       <c r="EM25" s="8">
-        <f t="shared" si="31"/>
-        <v>215.95473505245812</v>
+        <f t="shared" si="39"/>
+        <v>158.92947456109411</v>
       </c>
       <c r="EN25" s="8">
-        <f t="shared" si="31"/>
-        <v>213.79518770193354</v>
+        <f t="shared" si="39"/>
+        <v>157.34017981548317</v>
       </c>
       <c r="EO25" s="8">
-        <f t="shared" si="31"/>
-        <v>211.65723582491421</v>
+        <f t="shared" si="39"/>
+        <v>155.76677801732833</v>
       </c>
       <c r="EP25" s="8">
-        <f t="shared" si="31"/>
-        <v>209.54066346666508</v>
+        <f t="shared" si="39"/>
+        <v>154.20911023715504</v>
       </c>
       <c r="EQ25" s="8">
-        <f t="shared" si="31"/>
-        <v>207.44525683199842</v>
+        <f t="shared" si="39"/>
+        <v>152.66701913478349</v>
       </c>
       <c r="ER25" s="8">
-        <f t="shared" si="31"/>
-        <v>205.37080426367842</v>
+        <f t="shared" si="39"/>
+        <v>151.14034894343564</v>
       </c>
       <c r="ES25" s="8">
-        <f t="shared" si="31"/>
-        <v>203.31709622104165</v>
+        <f t="shared" si="39"/>
+        <v>149.6289454540013</v>
       </c>
     </row>
     <row r="26" spans="1:149" x14ac:dyDescent="0.3">
@@ -3179,105 +3212,97 @@
         <v>1</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" ref="C26:H26" si="32">1423.7</f>
+        <f t="shared" ref="C26:H26" si="40">1423.7</f>
         <v>1423.7</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1423.7</v>
       </c>
       <c r="E26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1423.7</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1423.7</v>
       </c>
       <c r="G26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1423.7</v>
       </c>
       <c r="H26" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>1423.7</v>
       </c>
       <c r="I26" s="2">
         <v>1029.0999999999999</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="13">
         <f>1032.2</f>
         <v>1032.2</v>
       </c>
-      <c r="K26" s="2"/>
+      <c r="K26" s="2">
+        <v>1027</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="N26" s="2">
-        <f t="shared" ref="N26:S26" si="33">1423.7</f>
+        <f t="shared" ref="N26:S26" si="41">1423.7</f>
         <v>1423.7</v>
       </c>
       <c r="O26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>1423.7</v>
       </c>
       <c r="P26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>1423.7</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>1423.7</v>
       </c>
       <c r="R26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>1423.7</v>
       </c>
       <c r="S26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>1423.7</v>
       </c>
       <c r="T26" s="2">
-        <f t="shared" ref="T26:AD26" si="34">1032.2</f>
+        <f t="shared" ref="T26:AD26" si="42">1032.2</f>
         <v>1032.2</v>
       </c>
       <c r="U26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="V26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="W26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="X26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="Y26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="Z26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="AA26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="AB26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="AC26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
       <c r="AD26" s="2">
-        <f t="shared" si="34"/>
-        <v>1032.2</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="27" spans="1:149" x14ac:dyDescent="0.3">
@@ -3285,106 +3310,109 @@
         <v>34</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" ref="C27:H27" si="35">C25/C26</f>
+        <f t="shared" ref="C27:H27" si="43">C25/C26</f>
         <v>8.9204186275198653E-3</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>1.4188382383929166E-2</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>2.6199339748542508E-2</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>5.3873709348879667E-2</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>9.8756760553487366E-2</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.15031256584954697</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" ref="I27:J27" si="36">I25/I26</f>
+        <f t="shared" ref="I27:K27" si="44">I25/I26</f>
         <v>0.2111553784860557</v>
       </c>
-      <c r="J27" s="16">
-        <f t="shared" si="36"/>
-        <v>0.24775617128463481</v>
-      </c>
-      <c r="K27" s="7"/>
+      <c r="J27" s="14">
+        <f t="shared" si="44"/>
+        <v>0.19317961635341996</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="44"/>
+        <v>0.1822784810126582</v>
+      </c>
       <c r="L27" s="7"/>
       <c r="N27" s="7">
-        <f t="shared" ref="N27:U27" si="37">N25/N26</f>
+        <f t="shared" ref="N27:U27" si="45">N25/N26</f>
         <v>7.2346702254688531E-3</v>
       </c>
       <c r="O27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>1.0254969445810223E-2</v>
       </c>
       <c r="P27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>2.1704010676406548E-2</v>
       </c>
       <c r="Q27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>2.3108801011449076E-2</v>
       </c>
       <c r="R27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>8.0073049097422244E-2</v>
       </c>
       <c r="S27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0.24906932640303439</v>
       </c>
       <c r="T27" s="7">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0.40370083317186584</v>
       </c>
       <c r="U27" s="7">
-        <f t="shared" si="37"/>
-        <v>0.46890405444681255</v>
+        <f t="shared" si="45"/>
+        <v>0.35504208373904583</v>
       </c>
       <c r="V27" s="7">
-        <f t="shared" ref="V27:AD27" si="38">V25/V26</f>
-        <v>0.5056553223696959</v>
+        <f t="shared" ref="V27:AD27" si="46">V25/V26</f>
+        <v>0.36454787891918217</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.53328770384857616</v>
+        <f t="shared" si="46"/>
+        <v>0.37599884009883172</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.55869772136356843</v>
+        <f t="shared" si="46"/>
+        <v>0.38755407607625625</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.57998260927453238</v>
+        <f t="shared" si="46"/>
+        <v>0.40808319622944877</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.6011183132544452</v>
+        <f t="shared" si="46"/>
+        <v>0.42934641225207526</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.61330118596803584</v>
+        <f t="shared" si="46"/>
+        <v>0.44189158343878221</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.62573253132935314</v>
+        <f t="shared" si="46"/>
+        <v>0.45480640533747296</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.63841746324715576</v>
+        <f t="shared" si="46"/>
+        <v>0.46810183338103517</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="38"/>
-        <v>0.65136120224205063</v>
+        <f t="shared" si="46"/>
+        <v>0.481789148983573</v>
       </c>
     </row>
     <row r="29" spans="1:149" x14ac:dyDescent="0.3">
@@ -3395,15 +3423,15 @@
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:J30" si="39">H3/F3-1</f>
+        <f t="shared" ref="H29:J30" si="47">H3/F3-1</f>
         <v>0.13734142305570862</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>0.12400212879191042</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>3.2492725509214448E-2</v>
       </c>
       <c r="K29" s="10"/>
@@ -3417,16 +3445,16 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>0.15137872819358478</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="47"/>
         <v>5.8015267175572482E-2</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="39"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="47"/>
+        <v>1.8572825024437911E-2</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
@@ -3439,15 +3467,15 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:J32" si="40">H6/F6-1</f>
+        <f t="shared" ref="H31:J32" si="48">H6/F6-1</f>
         <v>0.60364464692482933</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.55038759689922467</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.38920454545454519</v>
       </c>
       <c r="K31" s="10"/>
@@ -3461,16 +3489,16 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.58515283842794763</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>0.49196141479099675</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="40"/>
-        <v>0.35000000000000009</v>
+        <f t="shared" si="48"/>
+        <v>0.38980716253443548</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
@@ -3491,80 +3519,83 @@
         <v>0.55052672649239165</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" ref="F34:J34" si="41">F10/D10-1</f>
+        <f t="shared" ref="F34:K34" si="49">F10/D10-1</f>
         <v>0.4779314888010544</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.25364871665827882</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.2342322264319141</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="49"/>
         <v>0.18807707747892422</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="41"/>
-        <v>0.11854098952690517</v>
-      </c>
-      <c r="K34" s="10"/>
+        <f t="shared" si="49"/>
+        <v>0.11953773925604949</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="49"/>
+        <v>0.111674269302247</v>
+      </c>
       <c r="L34" s="10"/>
       <c r="O34" s="10"/>
       <c r="P34" s="10"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="10">
-        <f t="shared" ref="R34:AD34" si="42">R10/Q10-1</f>
+        <f t="shared" ref="R34:AD34" si="50">R10/Q10-1</f>
         <v>0.51116270762636185</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>0.24335184966316037</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>0.15199619771863127</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="42"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="50"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="42"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="50"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD34" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3579,81 +3610,84 @@
         <v>-16.583333333333329</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" ref="F35:J35" si="43">F11/D11-1</f>
+        <f t="shared" ref="F35:K35" si="51">F11/D11-1</f>
         <v>-74.625</v>
       </c>
       <c r="G35" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>10.288770053475936</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>1.3268251273344656</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0.42444339175746082</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="43"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="K35" s="10"/>
+        <f t="shared" si="51"/>
+        <v>7.1141919007661203E-2</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="51"/>
+        <v>-1.0974393082806788E-2</v>
+      </c>
       <c r="L35" s="10"/>
       <c r="O35" s="10"/>
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="10">
-        <f t="shared" ref="R35:AD35" si="44">R11/Q11-1</f>
+        <f t="shared" ref="R35:AD35" si="52">R11/Q11-1</f>
         <v>-49.749999999999993</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>2.5545787545787544</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>0.22485572959604272</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="44"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="52"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="44"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="52"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="44"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="44"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="52"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF35" t="s">
         <v>44</v>
@@ -3673,90 +3707,93 @@
         <v>0.63112504900039168</v>
       </c>
       <c r="F36" s="11">
-        <f t="shared" ref="F36:J36" si="45">F12/D12-1</f>
+        <f t="shared" ref="F36:K36" si="53">F12/D12-1</f>
         <v>0.87582781456953684</v>
       </c>
       <c r="G36" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>0.70463830809901462</v>
       </c>
       <c r="H36" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>0.46142983230361878</v>
       </c>
       <c r="I36" s="11">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>0.25842379811081351</v>
       </c>
       <c r="J36" s="11">
-        <f t="shared" si="45"/>
-        <v>0.17199661794902776</v>
-      </c>
-      <c r="K36" s="11"/>
+        <f t="shared" si="53"/>
+        <v>0.10351491726053896</v>
+      </c>
+      <c r="K36" s="11">
+        <f t="shared" si="53"/>
+        <v>7.0356262603630038E-2</v>
+      </c>
       <c r="L36" s="11"/>
       <c r="O36" s="11">
         <f>O12/N12-1</f>
         <v>0.70095559302979216</v>
       </c>
       <c r="P36" s="11">
-        <f t="shared" ref="P36:AD36" si="46">P12/O12-1</f>
+        <f t="shared" ref="P36:AD36" si="54">P12/O12-1</f>
         <v>0.3912756113681426</v>
       </c>
       <c r="Q36" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.32327790973871728</v>
       </c>
       <c r="R36" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.76377670077185411</v>
       </c>
       <c r="S36" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.56442092407897415</v>
       </c>
       <c r="T36" s="11">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v>0.17499349466562575</v>
       </c>
       <c r="U36" s="11">
-        <f t="shared" si="46"/>
-        <v>0.12987099988927042</v>
+        <f t="shared" si="54"/>
+        <v>7.7096667035765787E-2</v>
       </c>
       <c r="V36" s="11">
-        <f t="shared" si="46"/>
-        <v>0.10334895159824242</v>
+        <f t="shared" si="54"/>
+        <v>7.457317374060124E-2</v>
       </c>
       <c r="W36" s="11">
-        <f t="shared" si="46"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="54"/>
+        <v>5.8055611510251515E-2</v>
       </c>
       <c r="X36" s="11">
-        <f t="shared" si="46"/>
-        <v>4.3261721473221382E-2</v>
+        <f t="shared" si="54"/>
+        <v>4.4186165636945995E-2</v>
       </c>
       <c r="Y36" s="11">
-        <f t="shared" si="46"/>
-        <v>3.3347377039022019E-2</v>
+        <f t="shared" si="54"/>
+        <v>3.7132575784370347E-2</v>
       </c>
       <c r="Z36" s="11">
-        <f t="shared" si="46"/>
-        <v>2.6716653290570491E-2</v>
+        <f t="shared" si="54"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA36" s="11">
-        <f t="shared" si="46"/>
-        <v>2.000000000000024E-2</v>
+        <f t="shared" si="54"/>
+        <v>2.2847704344707287E-2</v>
       </c>
       <c r="AB36" s="11">
-        <f t="shared" si="46"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="54"/>
+        <v>2.2867617009442842E-2</v>
       </c>
       <c r="AC36" s="11">
-        <f t="shared" si="46"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="54"/>
+        <v>2.2887612698466064E-2</v>
       </c>
       <c r="AD36" s="11">
-        <f t="shared" si="46"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="54"/>
+        <v>2.2907690974547812E-2</v>
       </c>
       <c r="AF36" t="s">
         <v>45</v>
@@ -3770,55 +3807,58 @@
         <v>38</v>
       </c>
       <c r="C37" s="10">
-        <f t="shared" ref="C37:E37" si="47">(C10-(C15+C14))/C10</f>
+        <f t="shared" ref="C37:E37" si="55">(C10-(C15+C14))/C10</f>
         <v>0.67811158798283266</v>
       </c>
       <c r="D37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>0.6525032938076416</v>
       </c>
       <c r="E37" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>0.61323603422244588</v>
       </c>
       <c r="F37" s="10">
-        <f t="shared" ref="F37:I37" si="48">(F10-(F15+F14))/F10</f>
+        <f t="shared" ref="F37:I37" si="56">(F10-(F15+F14))/F10</f>
         <v>0.61600178292846008</v>
       </c>
       <c r="G37" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.66459253311922928</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.72408811845431564</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v>0.7340767021456327</v>
       </c>
       <c r="J37" s="10">
         <f>(J10-(J15+J14))/J10</f>
-        <v>0.73</v>
-      </c>
-      <c r="K37" s="10"/>
+        <v>0.71000000000000008</v>
+      </c>
+      <c r="K37" s="10">
+        <f>(K10-(K15+K14))/K10</f>
+        <v>0.72902735562310039</v>
+      </c>
       <c r="L37" s="10"/>
       <c r="O37" s="10"/>
       <c r="P37" s="10"/>
       <c r="Q37" s="10">
-        <f t="shared" ref="Q37:T37" si="49">(Q10-(Q15+Q14))/Q10</f>
+        <f t="shared" ref="Q37:T37" si="57">(Q10-(Q15+Q14))/Q10</f>
         <v>0.66422575459903554</v>
       </c>
       <c r="R37" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.61470275381160622</v>
       </c>
       <c r="S37" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.69591254752851717</v>
       </c>
       <c r="T37" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>0.72175922105784307</v>
       </c>
       <c r="U37" s="10"/>
@@ -3835,8 +3875,8 @@
         <v>46</v>
       </c>
       <c r="AG37" s="2">
-        <f>NPV(AG36,T25:ES25)</f>
-        <v>6387.2824952179935</v>
+        <f>NPV(AG36,U25:ES25)</f>
+        <v>4747.2688727064942</v>
       </c>
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.3">
@@ -3847,43 +3887,46 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10">
-        <f t="shared" ref="F38:I38" si="50">(F11-F13)/F11</f>
+        <f t="shared" ref="F38:I38" si="58">(F11-F13)/F11</f>
         <v>0.84380305602716477</v>
       </c>
       <c r="G38" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>0.74751302700142119</v>
       </c>
       <c r="H38" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>0.73878146661802258</v>
       </c>
       <c r="I38" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>0.7179913535084802</v>
       </c>
       <c r="J38" s="10">
         <f>(J11-J13)/J11</f>
-        <v>0.74</v>
-      </c>
-      <c r="K38" s="10"/>
+        <v>0.73978201634877394</v>
+      </c>
+      <c r="K38" s="10">
+        <f>(K11-K13)/K11</f>
+        <v>0.75353059852051107</v>
+      </c>
       <c r="L38" s="10"/>
       <c r="O38" s="10"/>
       <c r="P38" s="10"/>
       <c r="Q38" s="10">
-        <f t="shared" ref="Q38:T38" si="51">(Q11-Q13)/Q11</f>
+        <f t="shared" ref="Q38:T38" si="59">(Q11-Q13)/Q11</f>
         <v>1</v>
       </c>
       <c r="R38" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.86520146520146513</v>
       </c>
       <c r="S38" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.7425803792250617</v>
       </c>
       <c r="T38" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="59"/>
         <v>0.72875652027595494</v>
       </c>
       <c r="U38" s="10"/>
@@ -3901,7 +3944,7 @@
       </c>
       <c r="AG38" s="2">
         <f>Main!D8</f>
-        <v>5985.7</v>
+        <v>6226.5</v>
       </c>
     </row>
     <row r="39" spans="2:33" x14ac:dyDescent="0.3">
@@ -3909,38 +3952,41 @@
         <v>40</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" ref="C39:J39" si="52">C17/C12</f>
+        <f t="shared" ref="C39:J39" si="60">C17/C12</f>
         <v>0.6765974127793023</v>
       </c>
       <c r="D39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.65066225165562908</v>
       </c>
       <c r="E39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.63061763999038689</v>
       </c>
       <c r="F39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.66337157987643425</v>
       </c>
       <c r="G39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.68927111236430283</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.72895277207392195</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="60"/>
         <v>0.7286578534617969</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="52"/>
-        <v>0.73361588628624663</v>
-      </c>
-      <c r="K39" s="10"/>
+        <f t="shared" si="60"/>
+        <v>0.7195709281961471</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" ref="K39" si="61">K17/K12</f>
+        <v>0.73665480427046259</v>
+      </c>
       <c r="L39" s="10"/>
       <c r="N39" s="10">
         <f>N17/N12</f>
@@ -3951,71 +3997,71 @@
         <v>0.62161269001982822</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" ref="P39:AD39" si="53">P17/P12</f>
+        <f t="shared" ref="P39:AD39" si="62">P17/P12</f>
         <v>0.61876484560570066</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>0.66253814395979183</v>
       </c>
       <c r="R39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>0.64950132302055774</v>
       </c>
       <c r="S39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>0.71064272703616971</v>
       </c>
       <c r="T39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
         <v>0.72406156571808211</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="62"/>
+        <v>0.73</v>
+      </c>
+      <c r="V39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="V39" s="10">
-        <f t="shared" si="53"/>
+      <c r="W39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="W39" s="10">
-        <f t="shared" si="53"/>
+      <c r="X39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="X39" s="10">
-        <f t="shared" si="53"/>
+      <c r="Y39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="Y39" s="10">
-        <f t="shared" si="53"/>
+      <c r="Z39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="53"/>
+      <c r="AA39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="AA39" s="10">
-        <f t="shared" si="53"/>
+      <c r="AB39" s="10">
+        <f t="shared" si="62"/>
         <v>0.74</v>
       </c>
-      <c r="AB39" s="10">
-        <f t="shared" si="53"/>
-        <v>0.73999999999999988</v>
-      </c>
       <c r="AC39" s="10">
-        <f t="shared" si="53"/>
-        <v>0.73999999999999988</v>
+        <f t="shared" si="62"/>
+        <v>0.74</v>
       </c>
       <c r="AD39" s="10">
-        <f t="shared" si="53"/>
-        <v>0.73999999999999988</v>
+        <f t="shared" si="62"/>
+        <v>0.74</v>
       </c>
       <c r="AF39" t="s">
         <v>48</v>
       </c>
       <c r="AG39" s="2">
         <f>AG37+AG38</f>
-        <v>12372.982495217993</v>
+        <v>10973.768872706494</v>
       </c>
     </row>
     <row r="40" spans="2:33" x14ac:dyDescent="0.3">
@@ -4029,26 +4075,29 @@
         <v>0.41195795006570313</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" ref="F40:J40" si="54">F18/D18-1</f>
+        <f t="shared" ref="F40:K40" si="63">F18/D18-1</f>
         <v>0.65248226950354637</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>0.37971149371800839</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>0.14234620886981375</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="63"/>
         <v>0.2367622259696458</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="54"/>
-        <v>0.18999999999999995</v>
-      </c>
-      <c r="K40" s="10"/>
+        <f t="shared" si="63"/>
+        <v>0.25829680651221065</v>
+      </c>
+      <c r="K40" s="10">
+        <f t="shared" si="63"/>
+        <v>0.2705208617398418</v>
+      </c>
       <c r="L40" s="10"/>
       <c r="N40" s="10"/>
       <c r="O40" s="10">
@@ -4056,63 +4105,63 @@
         <v>0.6964824120603017</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" ref="P40:AD40" si="55">P18/O18-1</f>
+        <f t="shared" ref="P40:AD40" si="64">P18/O18-1</f>
         <v>0.2885071090047393</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.47770114942528719</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.53858120721841951</v>
       </c>
       <c r="S40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.24550050556117275</v>
       </c>
       <c r="T40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.24792985874330253</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="55"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="64"/>
+        <v>0.24</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="W40" s="10">
-        <f t="shared" si="55"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="64"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" si="55"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="64"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF40" t="s">
@@ -4120,7 +4169,7 @@
       </c>
       <c r="AG40" s="1">
         <f>AG39/AD26</f>
-        <v>11.987001061052114</v>
+        <v>10.685266672547707</v>
       </c>
     </row>
     <row r="41" spans="2:33" x14ac:dyDescent="0.3">
@@ -4128,38 +4177,41 @@
         <v>42</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41:J41" si="56">C21/C12</f>
+        <f t="shared" ref="C41:J41" si="65">C21/C12</f>
         <v>8.3496667973343902E-2</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>9.0728476821191922E-2</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>0.13217976447969232</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>0.18040600176522503</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>0.28704356407725928</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>0.36030921608889965</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="65"/>
         <v>0.3382254089177682</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="56"/>
-        <v>0.36353706497810984</v>
-      </c>
-      <c r="K41" s="10"/>
+        <f t="shared" si="65"/>
+        <v>0.30396234676007006</v>
+      </c>
+      <c r="K41" s="10">
+        <f t="shared" ref="K41" si="66">K21/K12</f>
+        <v>0.27778940757797782</v>
+      </c>
       <c r="L41" s="10"/>
       <c r="N41" s="10">
         <f>N21/N12</f>
@@ -4170,71 +4222,71 @@
         <v>7.666886979510909E-2</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" ref="P41:AD41" si="57">P21/P12</f>
+        <f t="shared" ref="P41:AD41" si="67">P21/P12</f>
         <v>0.10665083135391924</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>8.7416980793394439E-2</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>0.15998371667005906</v>
       </c>
       <c r="S41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>0.32650273224043719</v>
       </c>
       <c r="T41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>0.32089469604694931</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.3236915717720687</v>
+        <f t="shared" si="67"/>
+        <v>0.25773699890822288</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31603797334418154</v>
+        <f t="shared" si="67"/>
+        <v>0.24629579659857923</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31134255384285875</v>
+        <f t="shared" si="67"/>
+        <v>0.2400834987358737</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31253796886835594</v>
+        <f t="shared" si="67"/>
+        <v>0.23698496058572732</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31392266932810253</v>
+        <f t="shared" si="67"/>
+        <v>0.24044429931740963</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31685477456460359</v>
+        <f t="shared" si="67"/>
+        <v>0.24545081919846104</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31700095384686583</v>
+        <f t="shared" si="67"/>
+        <v>0.24698524931433302</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31714856625934623</v>
+        <f t="shared" si="67"/>
+        <v>0.24852607711574085</v>
       </c>
       <c r="AC41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31729762585234123</v>
+        <f t="shared" si="67"/>
+        <v>0.25007326891069237</v>
       </c>
       <c r="AD41" s="10">
-        <f t="shared" si="57"/>
-        <v>0.31744814681389499</v>
+        <f t="shared" si="67"/>
+        <v>0.25162679012008721</v>
       </c>
       <c r="AF41" t="s">
         <v>50</v>
       </c>
       <c r="AG41" s="1">
         <f>Main!D3</f>
-        <v>10.08</v>
+        <v>8.3949999999999996</v>
       </c>
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.3">
@@ -4242,38 +4294,41 @@
         <v>32</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" ref="C42:J42" si="58">C24/C23</f>
+        <f t="shared" ref="C42:J42" si="68">C24/C23</f>
         <v>0.32446808510638242</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.19521912350597645</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.27290448343079937</v>
       </c>
       <c r="F42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.19432773109243701</v>
       </c>
       <c r="G42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.27637673700463206</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.25461511668408215</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>0.25709401709401719</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="58"/>
-        <v>0.25</v>
-      </c>
-      <c r="K42" s="10"/>
+        <f t="shared" si="68"/>
+        <v>0.26771942710246044</v>
+      </c>
+      <c r="K42" s="10">
+        <f t="shared" ref="K42" si="69">K24/K23</f>
+        <v>0.26472898664571881</v>
+      </c>
       <c r="L42" s="10"/>
       <c r="N42" s="10">
         <f>N24/N23</f>
@@ -4284,63 +4339,63 @@
         <v>0.26999999999999985</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" ref="P42:AD42" si="59">P24/P23</f>
+        <f t="shared" ref="P42:AD42" si="70">P24/P23</f>
         <v>0.2481751824817518</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25056947608200431</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.2218430034129692</v>
       </c>
       <c r="S42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.26339842127129198</v>
       </c>
       <c r="T42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.26221671388101986</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="W42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="Z42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AA42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AB42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AC42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AD42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
       <c r="AF42" s="8" t="s">
@@ -4348,7 +4403,7 @@
       </c>
       <c r="AG42" s="11">
         <f>AG40/AG41-1</f>
-        <v>0.1891866131996145</v>
+        <v>0.27281318315041192</v>
       </c>
     </row>
     <row r="43" spans="2:33" x14ac:dyDescent="0.3">
@@ -4356,38 +4411,41 @@
         <v>43</v>
       </c>
       <c r="C43" s="10">
-        <f t="shared" ref="C43:J43" si="60">C25/C12</f>
+        <f t="shared" ref="C43:J43" si="71">C25/C12</f>
         <v>4.9784398275186326E-2</v>
       </c>
       <c r="D43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>6.6887417218542911E-2</v>
       </c>
       <c r="E43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>8.9641913001682214E-2</v>
       </c>
       <c r="F43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0.13539276257722857</v>
       </c>
       <c r="G43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0.19822360073311712</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0.25848532431453081</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="71"/>
         <v>0.24344611248039427</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="60"/>
-        <v>0.26356278908704156</v>
-      </c>
-      <c r="K43" s="10"/>
+        <f t="shared" si="71"/>
+        <v>0.21825744308231179</v>
+      </c>
+      <c r="K43" s="10">
+        <f t="shared" ref="K43" si="72">K25/K12</f>
+        <v>0.1959388737701486</v>
+      </c>
       <c r="L43" s="10"/>
       <c r="N43" s="10">
         <f>N25/N12</f>
@@ -4398,64 +4456,64 @@
         <v>4.8248512888301433E-2</v>
       </c>
       <c r="P43" s="10">
-        <f t="shared" ref="P43:AD43" si="61">P25/P12</f>
+        <f t="shared" ref="P43:AD43" si="73">P25/P12</f>
         <v>7.3396674584323043E-2</v>
       </c>
       <c r="Q43" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="73"/>
         <v>5.9055824807036521E-2</v>
       </c>
       <c r="R43" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="73"/>
         <v>0.11601872582943218</v>
       </c>
       <c r="S43" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="73"/>
         <v>0.23067915690866514</v>
       </c>
       <c r="T43" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="73"/>
         <v>0.23070534824493408</v>
       </c>
       <c r="U43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23716638989245739</v>
+        <f t="shared" si="73"/>
+        <v>0.18742596579098328</v>
       </c>
       <c r="V43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23179862267575424</v>
+        <f t="shared" si="73"/>
+        <v>0.17908883236926465</v>
       </c>
       <c r="W43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.22847256673508484</v>
+        <f t="shared" si="73"/>
+        <v>0.17457897511233944</v>
       </c>
       <c r="X43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.22943312357519649</v>
+        <f t="shared" si="73"/>
+        <v>0.17232957157903697</v>
       </c>
       <c r="Y43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23048774964869878</v>
+        <f t="shared" si="73"/>
+        <v>0.17496127546615645</v>
       </c>
       <c r="Z43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23267098532653704</v>
+        <f t="shared" si="73"/>
+        <v>0.17871616537694501</v>
       </c>
       <c r="AA43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23273189336081299</v>
+        <f t="shared" si="73"/>
+        <v>0.17982942443656474</v>
       </c>
       <c r="AB43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.2327933985326798</v>
+        <f t="shared" si="73"/>
+        <v>0.18094732514216738</v>
       </c>
       <c r="AC43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23285550669642774</v>
+        <f t="shared" si="73"/>
+        <v>0.18206984304955365</v>
       </c>
       <c r="AD43" s="10">
-        <f t="shared" si="61"/>
-        <v>0.23291822376374177</v>
+        <f t="shared" si="73"/>
+        <v>0.18319695307090991</v>
       </c>
       <c r="AF43" t="s">
         <v>52</v>
